--- a/人员数据自动化看板底表.xlsx
+++ b/人员数据自动化看板底表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6405" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="6855"/>
   </bookViews>
   <sheets>
     <sheet name="总人员" sheetId="1" r:id="rId1"/>
@@ -13,10 +13,12 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">总人员!$A$1:$R$505</definedName>
     <definedName name="categoryHidden14">[1]categoryHidden14!A1:A38</definedName>
+    <definedName name="Hidden000cdfc206468fca52c_1_18">[2]Hidden000cdfc206468fca52c!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6683" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7066" uniqueCount="855">
   <si>
     <t>序号</t>
   </si>
@@ -2459,6 +2461,174 @@
   </si>
   <si>
     <t>E04510</t>
+  </si>
+  <si>
+    <t>S00008</t>
+  </si>
+  <si>
+    <t>十角兽</t>
+  </si>
+  <si>
+    <t>总经理</t>
+  </si>
+  <si>
+    <t>S00081</t>
+  </si>
+  <si>
+    <t>业务部</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>电销二组</t>
+  </si>
+  <si>
+    <t>电销主管</t>
+  </si>
+  <si>
+    <t>S00090</t>
+  </si>
+  <si>
+    <t>客户服务部</t>
+  </si>
+  <si>
+    <t>客服组</t>
+  </si>
+  <si>
+    <t>财税顾问主管</t>
+  </si>
+  <si>
+    <t>S00099</t>
+  </si>
+  <si>
+    <t>电销一组</t>
+  </si>
+  <si>
+    <t>S00100</t>
+  </si>
+  <si>
+    <t>人力行政部</t>
+  </si>
+  <si>
+    <t>人力组</t>
+  </si>
+  <si>
+    <t>S00122</t>
+  </si>
+  <si>
+    <t>电销专员</t>
+  </si>
+  <si>
+    <t>S00123</t>
+  </si>
+  <si>
+    <t>S00125</t>
+  </si>
+  <si>
+    <t>业务咨询组</t>
+  </si>
+  <si>
+    <t>S00127</t>
+  </si>
+  <si>
+    <t>S00129</t>
+  </si>
+  <si>
+    <t>S00134</t>
+  </si>
+  <si>
+    <t>S00137</t>
+  </si>
+  <si>
+    <t>S00142</t>
+  </si>
+  <si>
+    <t>财税顾问</t>
+  </si>
+  <si>
+    <t>S00148</t>
+  </si>
+  <si>
+    <t>S00150</t>
+  </si>
+  <si>
+    <t>客户交付组</t>
+  </si>
+  <si>
+    <t>工商客服</t>
+  </si>
+  <si>
+    <t>S00155</t>
+  </si>
+  <si>
+    <t>S00160</t>
+  </si>
+  <si>
+    <t>S00163</t>
+  </si>
+  <si>
+    <t>S00166</t>
+  </si>
+  <si>
+    <t>产品运维组</t>
+  </si>
+  <si>
+    <t>产品顾问</t>
+  </si>
+  <si>
+    <t>S00167</t>
+  </si>
+  <si>
+    <t>S00210</t>
+  </si>
+  <si>
+    <t>S00222</t>
+  </si>
+  <si>
+    <t>S00226</t>
+  </si>
+  <si>
+    <t>总账产品顾问</t>
+  </si>
+  <si>
+    <t>S00230</t>
+  </si>
+  <si>
+    <t>工商注册专员</t>
+  </si>
+  <si>
+    <t>S00239</t>
+  </si>
+  <si>
+    <t>市场部</t>
+  </si>
+  <si>
+    <t>用户运营</t>
+  </si>
+  <si>
+    <t>S00251</t>
+  </si>
+  <si>
+    <t>续费专员</t>
+  </si>
+  <si>
+    <t>S00252</t>
+  </si>
+  <si>
+    <t>助贷顾问</t>
+  </si>
+  <si>
+    <t>S00253</t>
+  </si>
+  <si>
+    <t>S00091</t>
+  </si>
+  <si>
+    <t>S00254</t>
+  </si>
+  <si>
+    <t>S00255</t>
   </si>
   <si>
     <t>离职日期</t>
@@ -2471,7 +2641,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2481,8 +2651,9 @@
     <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="179" formatCode="[$-409]yyyy/mm/dd;@"/>
     <numFmt numFmtId="180" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="181" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2548,6 +2719,12 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2695,12 +2872,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2906,7 +3083,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2926,6 +3103,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3047,16 +3239,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
@@ -3065,122 +3254,125 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="7">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3330,6 +3522,33 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3438,6 +3657,21 @@
       <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="员工数据"/>
+      <sheetName val="Hidden000cdfc206468fca52c"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3692,8 +3926,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:R505"/>
+  <sheetPr/>
+  <dimension ref="A1:R536"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.3362831858407" customWidth="1"/>
@@ -3753,7 +3987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:18">
+    <row r="2" spans="1:18">
       <c r="A2" s="24"/>
       <c r="B2" s="11">
         <f>ROW()-1</f>
@@ -3798,7 +4032,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="3" ht="21" hidden="1" customHeight="1" spans="1:18">
+    <row r="3" ht="21" customHeight="1" spans="1:18">
       <c r="A3" s="25"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:B66" si="0">ROW()-1</f>
@@ -3845,7 +4079,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:18">
+    <row r="4" spans="1:18">
       <c r="A4" s="23"/>
       <c r="B4" s="11">
         <f t="shared" si="0"/>
@@ -3896,7 +4130,7 @@
         <v>42389</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:18">
+    <row r="5" spans="1:18">
       <c r="A5" s="23"/>
       <c r="B5" s="11">
         <f t="shared" si="0"/>
@@ -3945,7 +4179,7 @@
         <v>42416</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:18">
+    <row r="6" spans="1:18">
       <c r="A6" s="23"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -3992,7 +4226,7 @@
         <v>42494</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:18">
+    <row r="7" spans="1:18">
       <c r="A7" s="23"/>
       <c r="B7" s="11">
         <f t="shared" si="0"/>
@@ -4041,7 +4275,7 @@
         <v>42502</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:18">
+    <row r="8" spans="1:18">
       <c r="A8" s="23"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -4090,7 +4324,7 @@
         <v>42506</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:18">
+    <row r="9" spans="1:18">
       <c r="A9" s="23"/>
       <c r="B9" s="11">
         <f t="shared" si="0"/>
@@ -4139,7 +4373,7 @@
         <v>42552</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:18">
+    <row r="10" spans="1:18">
       <c r="A10" s="23"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -4188,7 +4422,7 @@
         <v>42557</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:18">
+    <row r="11" spans="1:18">
       <c r="A11" s="23"/>
       <c r="B11" s="11">
         <f t="shared" si="0"/>
@@ -4235,7 +4469,7 @@
         <v>42563</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:18">
+    <row r="12" spans="1:18">
       <c r="A12" s="23"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -4284,7 +4518,7 @@
         <v>42605</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:18">
+    <row r="13" spans="1:18">
       <c r="A13" s="23"/>
       <c r="B13" s="11">
         <f t="shared" si="0"/>
@@ -4331,7 +4565,7 @@
         <v>42838</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:18">
+    <row r="14" spans="1:18">
       <c r="A14" s="23"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -4384,7 +4618,7 @@
         <v>42857</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:18">
+    <row r="15" spans="1:18">
       <c r="A15" s="23"/>
       <c r="B15" s="11">
         <f t="shared" si="0"/>
@@ -4437,7 +4671,7 @@
         <v>42908</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:18">
+    <row r="16" spans="1:18">
       <c r="A16" s="23"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -4484,7 +4718,7 @@
         <v>42912</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:18">
+    <row r="17" spans="1:18">
       <c r="A17" s="23"/>
       <c r="B17" s="11">
         <f t="shared" si="0"/>
@@ -4539,7 +4773,7 @@
         <v>42922</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:18">
+    <row r="18" spans="1:18">
       <c r="A18" s="23"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
@@ -4588,7 +4822,7 @@
         <v>42922</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:18">
+    <row r="19" spans="1:18">
       <c r="A19" s="23"/>
       <c r="B19" s="11">
         <f t="shared" si="0"/>
@@ -4637,7 +4871,7 @@
         <v>42954</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:18">
+    <row r="20" spans="1:18">
       <c r="A20" s="24"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
@@ -4686,7 +4920,7 @@
         <v>42954</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:18">
+    <row r="21" spans="1:18">
       <c r="A21" s="24"/>
       <c r="B21" s="11">
         <f t="shared" si="0"/>
@@ -4735,7 +4969,7 @@
         <v>42955</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:18">
+    <row r="22" spans="1:18">
       <c r="A22" s="23"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
@@ -4790,7 +5024,7 @@
         <v>42972</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:18">
+    <row r="23" spans="1:18">
       <c r="A23" s="23"/>
       <c r="B23" s="11">
         <f t="shared" si="0"/>
@@ -4845,7 +5079,7 @@
         <v>43027</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:18">
+    <row r="24" spans="1:18">
       <c r="A24" s="23"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
@@ -4900,7 +5134,7 @@
         <v>43031</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:18">
+    <row r="25" spans="1:18">
       <c r="A25" s="23"/>
       <c r="B25" s="11">
         <f t="shared" si="0"/>
@@ -4953,7 +5187,7 @@
         <v>43080</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:18">
+    <row r="26" spans="1:18">
       <c r="A26" s="23"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
@@ -5006,7 +5240,7 @@
         <v>43088</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:18">
+    <row r="27" spans="1:18">
       <c r="A27" s="23"/>
       <c r="B27" s="11">
         <f t="shared" si="0"/>
@@ -5059,7 +5293,7 @@
         <v>43091</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:18">
+    <row r="28" spans="1:18">
       <c r="A28" s="23"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
@@ -5108,7 +5342,7 @@
         <v>43096</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:18">
+    <row r="29" spans="1:18">
       <c r="A29" s="23"/>
       <c r="B29" s="11">
         <f t="shared" si="0"/>
@@ -5163,7 +5397,7 @@
         <v>43115</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:18">
+    <row r="30" spans="1:18">
       <c r="A30" s="23"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
@@ -5210,7 +5444,7 @@
         <v>43124</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:18">
+    <row r="31" spans="1:18">
       <c r="A31" s="23"/>
       <c r="B31" s="11">
         <f t="shared" si="0"/>
@@ -5257,7 +5491,7 @@
         <v>43185</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:18">
+    <row r="32" spans="1:18">
       <c r="A32" s="23"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
@@ -5312,7 +5546,7 @@
         <v>43198</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:18">
+    <row r="33" spans="1:18">
       <c r="A33" s="23"/>
       <c r="B33" s="11">
         <f t="shared" si="0"/>
@@ -5367,7 +5601,7 @@
         <v>43213</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:18">
+    <row r="34" spans="1:18">
       <c r="A34" s="24"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
@@ -5416,7 +5650,7 @@
         <v>43217</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:18">
+    <row r="35" spans="1:18">
       <c r="A35" s="23"/>
       <c r="B35" s="11">
         <f t="shared" si="0"/>
@@ -5471,7 +5705,7 @@
         <v>43227</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:18">
+    <row r="36" spans="1:18">
       <c r="A36" s="23"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
@@ -5518,7 +5752,7 @@
         <v>43229</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:18">
+    <row r="37" spans="1:18">
       <c r="A37" s="23"/>
       <c r="B37" s="11">
         <f t="shared" si="0"/>
@@ -5573,7 +5807,7 @@
         <v>43230</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:18">
+    <row r="38" spans="1:18">
       <c r="A38" s="23"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
@@ -5620,7 +5854,7 @@
         <v>43241</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:18">
+    <row r="39" spans="1:18">
       <c r="A39" s="23"/>
       <c r="B39" s="11">
         <f t="shared" si="0"/>
@@ -5673,7 +5907,7 @@
         <v>43237</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:18">
+    <row r="40" spans="1:18">
       <c r="A40" s="23"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
@@ -5720,7 +5954,7 @@
         <v>43244</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:18">
+    <row r="41" spans="1:18">
       <c r="A41" s="23"/>
       <c r="B41" s="11">
         <f t="shared" si="0"/>
@@ -5769,7 +6003,7 @@
         <v>43248</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:18">
+    <row r="42" spans="1:18">
       <c r="A42" s="23"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
@@ -5824,7 +6058,7 @@
         <v>43251</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:18">
+    <row r="43" spans="1:18">
       <c r="A43" s="23"/>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
@@ -5877,7 +6111,7 @@
         <v>43252</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:18">
+    <row r="44" spans="1:18">
       <c r="A44" s="23"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
@@ -5926,7 +6160,7 @@
         <v>43283</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:18">
+    <row r="45" spans="1:18">
       <c r="A45" s="23"/>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
@@ -5977,7 +6211,7 @@
         <v>43304</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:18">
+    <row r="46" spans="1:18">
       <c r="A46" s="23"/>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
@@ -6026,7 +6260,7 @@
         <v>43311</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:18">
+    <row r="47" spans="1:18">
       <c r="A47" s="23"/>
       <c r="B47" s="11">
         <f t="shared" si="0"/>
@@ -6081,7 +6315,7 @@
         <v>43311</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:18">
+    <row r="48" spans="1:18">
       <c r="A48" s="23"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
@@ -6136,7 +6370,7 @@
         <v>43346</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:18">
+    <row r="49" spans="1:18">
       <c r="A49" s="23"/>
       <c r="B49" s="11">
         <f t="shared" si="0"/>
@@ -6185,7 +6419,7 @@
         <v>43353</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:18">
+    <row r="50" spans="1:18">
       <c r="A50" s="23"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
@@ -6236,7 +6470,7 @@
         <v>43354</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:18">
+    <row r="51" spans="1:18">
       <c r="A51" s="23"/>
       <c r="B51" s="11">
         <f t="shared" si="0"/>
@@ -6291,7 +6525,7 @@
         <v>43363</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:18">
+    <row r="52" spans="1:18">
       <c r="A52" s="23"/>
       <c r="B52" s="11">
         <f t="shared" si="0"/>
@@ -6338,7 +6572,7 @@
         <v>43383</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:18">
+    <row r="53" spans="1:18">
       <c r="A53" s="23"/>
       <c r="B53" s="11">
         <f t="shared" si="0"/>
@@ -6385,7 +6619,7 @@
         <v>43383</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:18">
+    <row r="54" spans="1:18">
       <c r="A54" s="23"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
@@ -6440,7 +6674,7 @@
         <v>43416</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:18">
+    <row r="55" spans="1:18">
       <c r="A55" s="24"/>
       <c r="B55" s="11">
         <f t="shared" si="0"/>
@@ -6493,7 +6727,7 @@
         <v>43425</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:18">
+    <row r="56" spans="1:18">
       <c r="A56" s="23"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
@@ -6540,7 +6774,7 @@
         <v>43528</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:18">
+    <row r="57" spans="1:18">
       <c r="A57" s="23"/>
       <c r="B57" s="11">
         <f t="shared" si="0"/>
@@ -6589,7 +6823,7 @@
         <v>43528</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:18">
+    <row r="58" spans="1:18">
       <c r="A58" s="23"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
@@ -6640,7 +6874,7 @@
         <v>43528</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:18">
+    <row r="59" spans="1:18">
       <c r="A59" s="23"/>
       <c r="B59" s="11">
         <f t="shared" si="0"/>
@@ -6687,7 +6921,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:18">
+    <row r="60" spans="1:18">
       <c r="A60" s="23"/>
       <c r="B60" s="11">
         <f t="shared" si="0"/>
@@ -6742,7 +6976,7 @@
         <v>43570</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:18">
+    <row r="61" spans="1:18">
       <c r="A61" s="23"/>
       <c r="B61" s="11">
         <f t="shared" si="0"/>
@@ -6791,7 +7025,7 @@
         <v>43570</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:18">
+    <row r="62" spans="1:18">
       <c r="A62" s="24"/>
       <c r="B62" s="11">
         <f t="shared" si="0"/>
@@ -6846,7 +7080,7 @@
         <v>43584</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:18">
+    <row r="63" spans="1:18">
       <c r="A63" s="23"/>
       <c r="B63" s="11">
         <f t="shared" si="0"/>
@@ -6895,7 +7129,7 @@
         <v>43598</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:18">
+    <row r="64" spans="1:18">
       <c r="A64" s="23"/>
       <c r="B64" s="11">
         <f t="shared" si="0"/>
@@ -6950,7 +7184,7 @@
         <v>43605</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:18">
+    <row r="65" spans="1:18">
       <c r="A65" s="23"/>
       <c r="B65" s="11">
         <f t="shared" si="0"/>
@@ -7005,7 +7239,7 @@
         <v>43612</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:18">
+    <row r="66" spans="1:18">
       <c r="A66" s="23"/>
       <c r="B66" s="11">
         <f t="shared" ref="B66:B129" si="1">ROW()-1</f>
@@ -7058,7 +7292,7 @@
         <v>43615</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:18">
+    <row r="67" spans="1:18">
       <c r="A67" s="23"/>
       <c r="B67" s="11">
         <f t="shared" si="1"/>
@@ -7111,7 +7345,7 @@
         <v>43615</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:18">
+    <row r="68" spans="1:18">
       <c r="A68" s="23"/>
       <c r="B68" s="11">
         <f t="shared" si="1"/>
@@ -7162,7 +7396,7 @@
         <v>43619</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:18">
+    <row r="69" spans="1:18">
       <c r="A69" s="23"/>
       <c r="B69" s="11">
         <f t="shared" si="1"/>
@@ -7215,7 +7449,7 @@
         <v>43630</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:18">
+    <row r="70" spans="1:18">
       <c r="A70" s="23"/>
       <c r="B70" s="11">
         <f t="shared" si="1"/>
@@ -7268,7 +7502,7 @@
         <v>43633</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:18">
+    <row r="71" spans="1:18">
       <c r="A71" s="23"/>
       <c r="B71" s="11">
         <f t="shared" si="1"/>
@@ -7315,7 +7549,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:18">
+    <row r="72" spans="1:18">
       <c r="A72" s="23"/>
       <c r="B72" s="11">
         <f t="shared" si="1"/>
@@ -7368,7 +7602,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:18">
+    <row r="73" spans="1:18">
       <c r="A73" s="23"/>
       <c r="B73" s="11">
         <f t="shared" si="1"/>
@@ -7417,7 +7651,7 @@
         <v>43647</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:18">
+    <row r="74" spans="1:18">
       <c r="A74" s="23"/>
       <c r="B74" s="11">
         <f t="shared" si="1"/>
@@ -7466,7 +7700,7 @@
         <v>43647</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:18">
+    <row r="75" spans="1:18">
       <c r="A75" s="23"/>
       <c r="B75" s="11">
         <f t="shared" si="1"/>
@@ -7515,7 +7749,7 @@
         <v>43658</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:18">
+    <row r="76" spans="1:18">
       <c r="A76" s="23"/>
       <c r="B76" s="11">
         <f t="shared" si="1"/>
@@ -7568,7 +7802,7 @@
         <v>43661</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:18">
+    <row r="77" spans="1:18">
       <c r="A77" s="23"/>
       <c r="B77" s="11">
         <f t="shared" si="1"/>
@@ -7615,7 +7849,7 @@
         <v>43670</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:18">
+    <row r="78" spans="1:18">
       <c r="A78" s="23" t="s">
         <v>228</v>
       </c>
@@ -7672,7 +7906,7 @@
         <v>43678</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:18">
+    <row r="79" spans="1:18">
       <c r="A79" s="23"/>
       <c r="B79" s="11">
         <f t="shared" si="1"/>
@@ -7721,7 +7955,7 @@
         <v>43679</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:18">
+    <row r="80" spans="1:18">
       <c r="A80" s="23"/>
       <c r="B80" s="11">
         <f t="shared" si="1"/>
@@ -7770,7 +8004,7 @@
         <v>43679</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:18">
+    <row r="81" spans="1:18">
       <c r="A81" s="23"/>
       <c r="B81" s="11">
         <f t="shared" si="1"/>
@@ -7819,7 +8053,7 @@
         <v>43682</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:18">
+    <row r="82" spans="1:18">
       <c r="A82" s="23"/>
       <c r="B82" s="11">
         <f t="shared" si="1"/>
@@ -7874,7 +8108,7 @@
         <v>43696</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:18">
+    <row r="83" spans="1:18">
       <c r="A83" s="23"/>
       <c r="B83" s="11">
         <f t="shared" si="1"/>
@@ -7925,7 +8159,7 @@
         <v>43717</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:18">
+    <row r="84" spans="1:18">
       <c r="A84" s="23"/>
       <c r="B84" s="11">
         <f t="shared" si="1"/>
@@ -7980,7 +8214,7 @@
         <v>43726</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:18">
+    <row r="85" spans="1:18">
       <c r="A85" s="23"/>
       <c r="B85" s="11">
         <f t="shared" si="1"/>
@@ -8029,7 +8263,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:18">
+    <row r="86" spans="1:18">
       <c r="A86" s="23"/>
       <c r="B86" s="11">
         <f t="shared" si="1"/>
@@ -8078,7 +8312,7 @@
         <v>43738</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:18">
+    <row r="87" spans="1:18">
       <c r="A87" s="23"/>
       <c r="B87" s="11">
         <f t="shared" si="1"/>
@@ -8127,7 +8361,7 @@
         <v>43747</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:18">
+    <row r="88" spans="1:18">
       <c r="A88" s="23"/>
       <c r="B88" s="11">
         <f t="shared" si="1"/>
@@ -8182,7 +8416,7 @@
         <v>43753</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:18">
+    <row r="89" spans="1:18">
       <c r="A89" s="23"/>
       <c r="B89" s="11">
         <f t="shared" si="1"/>
@@ -8235,7 +8469,7 @@
         <v>43754</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:18">
+    <row r="90" spans="1:18">
       <c r="A90" s="23"/>
       <c r="B90" s="11">
         <f t="shared" si="1"/>
@@ -8284,7 +8518,7 @@
         <v>43766</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:18">
+    <row r="91" spans="1:18">
       <c r="A91" s="23"/>
       <c r="B91" s="11">
         <f t="shared" si="1"/>
@@ -8333,7 +8567,7 @@
         <v>43766</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:18">
+    <row r="92" spans="1:18">
       <c r="A92" s="23"/>
       <c r="B92" s="11">
         <f t="shared" si="1"/>
@@ -8382,7 +8616,7 @@
         <v>43770</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:18">
+    <row r="93" spans="1:18">
       <c r="A93" s="23"/>
       <c r="B93" s="11">
         <f t="shared" si="1"/>
@@ -8429,7 +8663,7 @@
         <v>43782</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:18">
+    <row r="94" spans="1:18">
       <c r="A94" s="23"/>
       <c r="B94" s="11">
         <f t="shared" si="1"/>
@@ -8476,7 +8710,7 @@
         <v>43784</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:18">
+    <row r="95" spans="1:18">
       <c r="A95" s="23"/>
       <c r="B95" s="11">
         <f t="shared" si="1"/>
@@ -8529,7 +8763,7 @@
         <v>43788</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:18">
+    <row r="96" spans="1:18">
       <c r="A96" s="23"/>
       <c r="B96" s="11">
         <f t="shared" si="1"/>
@@ -8576,7 +8810,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:18">
+    <row r="97" spans="1:18">
       <c r="A97" s="23"/>
       <c r="B97" s="11">
         <f t="shared" si="1"/>
@@ -8623,7 +8857,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:18">
+    <row r="98" spans="1:18">
       <c r="A98" s="23"/>
       <c r="B98" s="11">
         <f t="shared" si="1"/>
@@ -8678,7 +8912,7 @@
         <v>43815</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:18">
+    <row r="99" spans="1:18">
       <c r="A99" s="23"/>
       <c r="B99" s="11">
         <f t="shared" si="1"/>
@@ -8725,7 +8959,7 @@
         <v>43822</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:18">
+    <row r="100" spans="1:18">
       <c r="A100" s="23"/>
       <c r="B100" s="11">
         <f t="shared" si="1"/>
@@ -8772,7 +9006,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:18">
+    <row r="101" spans="1:18">
       <c r="A101" s="23"/>
       <c r="B101" s="11">
         <f t="shared" si="1"/>
@@ -8821,7 +9055,7 @@
         <v>43892</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:18">
+    <row r="102" spans="1:18">
       <c r="A102" s="23"/>
       <c r="B102" s="11">
         <f t="shared" si="1"/>
@@ -8870,7 +9104,7 @@
         <v>43899</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:18">
+    <row r="103" spans="1:18">
       <c r="A103" s="23"/>
       <c r="B103" s="11">
         <f t="shared" si="1"/>
@@ -8925,7 +9159,7 @@
         <v>43900</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:18">
+    <row r="104" spans="1:18">
       <c r="A104" s="23"/>
       <c r="B104" s="11">
         <f t="shared" si="1"/>
@@ -8974,7 +9208,7 @@
         <v>43906</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:18">
+    <row r="105" spans="1:18">
       <c r="A105" s="23"/>
       <c r="B105" s="11">
         <f t="shared" si="1"/>
@@ -9023,7 +9257,7 @@
         <v>43913</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:18">
+    <row r="106" spans="1:18">
       <c r="A106" s="24"/>
       <c r="B106" s="11">
         <f t="shared" si="1"/>
@@ -9074,7 +9308,7 @@
         <v>43913</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:18">
+    <row r="107" spans="1:18">
       <c r="A107" s="23"/>
       <c r="B107" s="11">
         <f t="shared" si="1"/>
@@ -9129,7 +9363,7 @@
         <v>43915</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:18">
+    <row r="108" spans="1:18">
       <c r="A108" s="23"/>
       <c r="B108" s="11">
         <f t="shared" si="1"/>
@@ -9180,7 +9414,7 @@
         <v>43920</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:18">
+    <row r="109" spans="1:18">
       <c r="A109" s="23"/>
       <c r="B109" s="11">
         <f t="shared" si="1"/>
@@ -9229,7 +9463,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:18">
+    <row r="110" spans="1:18">
       <c r="A110" s="23"/>
       <c r="B110" s="11">
         <f t="shared" si="1"/>
@@ -9282,7 +9516,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:18">
+    <row r="111" spans="1:18">
       <c r="A111" s="23"/>
       <c r="B111" s="11">
         <f t="shared" si="1"/>
@@ -9337,7 +9571,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:18">
+    <row r="112" spans="1:18">
       <c r="A112" s="23"/>
       <c r="B112" s="11">
         <f t="shared" si="1"/>
@@ -9392,7 +9626,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:18">
+    <row r="113" spans="1:18">
       <c r="A113" s="23"/>
       <c r="B113" s="11">
         <f t="shared" si="1"/>
@@ -9447,7 +9681,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:18">
+    <row r="114" spans="1:18">
       <c r="A114" s="23"/>
       <c r="B114" s="11">
         <f t="shared" si="1"/>
@@ -9500,7 +9734,7 @@
         <v>43935</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:18">
+    <row r="115" spans="1:18">
       <c r="A115" s="23"/>
       <c r="B115" s="11">
         <f t="shared" si="1"/>
@@ -9549,7 +9783,7 @@
         <v>43938</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:18">
+    <row r="116" spans="1:18">
       <c r="A116" s="23"/>
       <c r="B116" s="11">
         <f t="shared" si="1"/>
@@ -9604,7 +9838,7 @@
         <v>43938</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:18">
+    <row r="117" spans="1:18">
       <c r="A117" s="23"/>
       <c r="B117" s="11">
         <f t="shared" si="1"/>
@@ -9655,7 +9889,7 @@
         <v>43941</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:18">
+    <row r="118" spans="1:18">
       <c r="A118" s="23"/>
       <c r="B118" s="11">
         <f t="shared" si="1"/>
@@ -9708,7 +9942,7 @@
         <v>43943</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:18">
+    <row r="119" spans="1:18">
       <c r="A119" s="24"/>
       <c r="B119" s="11">
         <f t="shared" si="1"/>
@@ -9763,7 +9997,7 @@
         <v>43948</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:18">
+    <row r="120" spans="1:18">
       <c r="A120" s="23"/>
       <c r="B120" s="11">
         <f t="shared" si="1"/>
@@ -9810,7 +10044,7 @@
         <v>43948</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:18">
+    <row r="121" spans="1:18">
       <c r="A121" s="23"/>
       <c r="B121" s="11">
         <f t="shared" si="1"/>
@@ -9857,7 +10091,7 @@
         <v>43960</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:18">
+    <row r="122" spans="1:18">
       <c r="A122" s="23"/>
       <c r="B122" s="11">
         <f t="shared" si="1"/>
@@ -9906,7 +10140,7 @@
         <v>43948</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:18">
+    <row r="123" spans="1:18">
       <c r="A123" s="23"/>
       <c r="B123" s="11">
         <f t="shared" si="1"/>
@@ -9955,7 +10189,7 @@
         <v>43957</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:18">
+    <row r="124" spans="1:18">
       <c r="A124" s="23"/>
       <c r="B124" s="11">
         <f t="shared" si="1"/>
@@ -10002,7 +10236,7 @@
         <v>43957</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:18">
+    <row r="125" spans="1:18">
       <c r="A125" s="23"/>
       <c r="B125" s="11">
         <f t="shared" si="1"/>
@@ -10049,7 +10283,7 @@
         <v>43957</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:18">
+    <row r="126" spans="1:18">
       <c r="A126" s="23"/>
       <c r="B126" s="11">
         <f t="shared" si="1"/>
@@ -10100,7 +10334,7 @@
         <v>43957</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:18">
+    <row r="127" spans="1:18">
       <c r="A127" s="23"/>
       <c r="B127" s="11">
         <f t="shared" si="1"/>
@@ -10149,7 +10383,7 @@
         <v>43964</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:18">
+    <row r="128" spans="1:18">
       <c r="A128" s="23"/>
       <c r="B128" s="11">
         <f t="shared" si="1"/>
@@ -10202,7 +10436,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:18">
+    <row r="129" spans="1:18">
       <c r="A129" s="30"/>
       <c r="B129" s="11">
         <f t="shared" si="1"/>
@@ -10251,7 +10485,7 @@
         <v>43976</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:18">
+    <row r="130" spans="1:18">
       <c r="A130" s="23"/>
       <c r="B130" s="11">
         <f t="shared" ref="B130:B152" si="2">ROW()-1</f>
@@ -10304,7 +10538,7 @@
         <v>43980</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:18">
+    <row r="131" spans="1:18">
       <c r="A131" s="23"/>
       <c r="B131" s="11">
         <f t="shared" si="2"/>
@@ -10351,7 +10585,7 @@
         <v>43983</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:18">
+    <row r="132" spans="1:18">
       <c r="A132" s="23"/>
       <c r="B132" s="11">
         <f t="shared" si="2"/>
@@ -10400,7 +10634,7 @@
         <v>43983</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:18">
+    <row r="133" spans="1:18">
       <c r="A133" s="23"/>
       <c r="B133" s="11">
         <f t="shared" si="2"/>
@@ -10449,7 +10683,7 @@
         <v>43983</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:18">
+    <row r="134" spans="1:18">
       <c r="A134" s="23"/>
       <c r="B134" s="11">
         <f t="shared" si="2"/>
@@ -10498,7 +10732,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:18">
+    <row r="135" spans="1:18">
       <c r="A135" s="23"/>
       <c r="B135" s="11">
         <f t="shared" si="2"/>
@@ -10553,7 +10787,7 @@
         <v>43984</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:18">
+    <row r="136" spans="1:18">
       <c r="A136" s="23"/>
       <c r="B136" s="11">
         <f t="shared" si="2"/>
@@ -10606,7 +10840,7 @@
         <v>43990</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:18">
+    <row r="137" spans="1:18">
       <c r="A137" s="30"/>
       <c r="B137" s="11">
         <f t="shared" si="2"/>
@@ -10655,7 +10889,7 @@
         <v>43992</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:18">
+    <row r="138" spans="1:18">
       <c r="A138" s="23"/>
       <c r="B138" s="11">
         <f t="shared" si="2"/>
@@ -10704,7 +10938,7 @@
         <v>43994</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:18">
+    <row r="139" spans="1:18">
       <c r="A139" s="23"/>
       <c r="B139" s="11">
         <f t="shared" si="2"/>
@@ -10755,7 +10989,7 @@
         <v>43998</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:18">
+    <row r="140" spans="1:18">
       <c r="A140" s="23"/>
       <c r="B140" s="11">
         <f t="shared" si="2"/>
@@ -10808,7 +11042,7 @@
         <v>44004</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:18">
+    <row r="141" spans="1:18">
       <c r="A141" s="23"/>
       <c r="B141" s="11">
         <f t="shared" si="2"/>
@@ -10861,7 +11095,7 @@
         <v>44004</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:18">
+    <row r="142" spans="1:18">
       <c r="A142" s="23"/>
       <c r="B142" s="11">
         <f t="shared" si="2"/>
@@ -10910,7 +11144,7 @@
         <v>44006</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:18">
+    <row r="143" spans="1:18">
       <c r="A143" s="23"/>
       <c r="B143" s="11">
         <f t="shared" si="2"/>
@@ -10961,7 +11195,7 @@
         <v>44010</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:18">
+    <row r="144" spans="1:18">
       <c r="A144" s="30"/>
       <c r="B144" s="11">
         <f t="shared" si="2"/>
@@ -11008,7 +11242,7 @@
         <v>44011</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:18">
+    <row r="145" spans="1:18">
       <c r="A145" s="23"/>
       <c r="B145" s="11">
         <f t="shared" si="2"/>
@@ -11055,7 +11289,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:18">
+    <row r="146" spans="1:18">
       <c r="A146" s="23"/>
       <c r="B146" s="11">
         <f t="shared" si="2"/>
@@ -11106,7 +11340,7 @@
         <v>44018</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:18">
+    <row r="147" spans="1:18">
       <c r="A147" s="23"/>
       <c r="B147" s="11">
         <f t="shared" si="2"/>
@@ -11161,7 +11395,7 @@
         <v>44018</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:18">
+    <row r="148" spans="1:18">
       <c r="A148" s="23"/>
       <c r="B148" s="11">
         <f t="shared" si="2"/>
@@ -11212,7 +11446,7 @@
         <v>44019</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:18">
+    <row r="149" spans="1:18">
       <c r="A149" s="23"/>
       <c r="B149" s="11">
         <f t="shared" si="2"/>
@@ -11259,7 +11493,7 @@
         <v>44020</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:18">
+    <row r="150" spans="1:18">
       <c r="A150" s="23"/>
       <c r="B150" s="11">
         <f t="shared" si="2"/>
@@ -11314,7 +11548,7 @@
         <v>44027</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:18">
+    <row r="151" spans="1:18">
       <c r="A151" s="23"/>
       <c r="B151" s="11">
         <f t="shared" si="2"/>
@@ -11361,7 +11595,7 @@
         <v>44029</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:18">
+    <row r="152" spans="1:18">
       <c r="A152" s="23"/>
       <c r="B152" s="11">
         <f t="shared" si="2"/>
@@ -11406,7 +11640,7 @@
         <v>44046</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:18">
+    <row r="153" spans="1:18">
       <c r="A153" s="23"/>
       <c r="B153" s="11">
         <f t="shared" ref="B153:B216" si="3">ROW()-1</f>
@@ -11461,7 +11695,7 @@
         <v>44055</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:18">
+    <row r="154" spans="1:18">
       <c r="A154" s="23"/>
       <c r="B154" s="11">
         <f t="shared" si="3"/>
@@ -11514,7 +11748,7 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="1:18">
+    <row r="155" spans="1:18">
       <c r="A155" s="23"/>
       <c r="B155" s="11">
         <f t="shared" si="3"/>
@@ -11563,7 +11797,7 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:18">
+    <row r="156" spans="1:18">
       <c r="A156" s="23"/>
       <c r="B156" s="11">
         <f t="shared" si="3"/>
@@ -11616,7 +11850,7 @@
         <v>44074</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:18">
+    <row r="157" spans="1:18">
       <c r="A157" s="23"/>
       <c r="B157" s="11">
         <f t="shared" si="3"/>
@@ -11663,7 +11897,7 @@
         <v>44075</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:18">
+    <row r="158" spans="1:18">
       <c r="A158" s="23"/>
       <c r="B158" s="11">
         <f t="shared" si="3"/>
@@ -11712,7 +11946,7 @@
         <v>44075</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:18">
+    <row r="159" spans="1:18">
       <c r="A159" s="23"/>
       <c r="B159" s="11">
         <f t="shared" si="3"/>
@@ -11767,7 +12001,7 @@
         <v>44084</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:18">
+    <row r="160" spans="1:18">
       <c r="A160" s="23"/>
       <c r="B160" s="11">
         <f t="shared" si="3"/>
@@ -11816,7 +12050,7 @@
         <v>44088</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:18">
+    <row r="161" spans="1:18">
       <c r="A161" s="23"/>
       <c r="B161" s="11">
         <f t="shared" si="3"/>
@@ -11869,7 +12103,7 @@
         <v>44119</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:18">
+    <row r="162" spans="1:18">
       <c r="A162" s="23"/>
       <c r="B162" s="11">
         <f t="shared" si="3"/>
@@ -11922,7 +12156,7 @@
         <v>44120</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:18">
+    <row r="163" spans="1:18">
       <c r="A163" s="23"/>
       <c r="B163" s="11">
         <f t="shared" si="3"/>
@@ -11971,7 +12205,7 @@
         <v>44137</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:18">
+    <row r="164" spans="1:18">
       <c r="A164" s="23"/>
       <c r="B164" s="11">
         <f t="shared" si="3"/>
@@ -12024,7 +12258,7 @@
         <v>44140</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:18">
+    <row r="165" spans="1:18">
       <c r="A165" s="23"/>
       <c r="B165" s="11">
         <f t="shared" si="3"/>
@@ -12077,7 +12311,7 @@
         <v>44147</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:18">
+    <row r="166" spans="1:18">
       <c r="A166" s="23"/>
       <c r="B166" s="11">
         <f t="shared" si="3"/>
@@ -12128,7 +12362,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:18">
+    <row r="167" spans="1:18">
       <c r="A167" s="23"/>
       <c r="B167" s="11">
         <f t="shared" si="3"/>
@@ -12175,7 +12409,7 @@
         <v>44168</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:18">
+    <row r="168" spans="1:18">
       <c r="A168" s="23"/>
       <c r="B168" s="11">
         <f t="shared" si="3"/>
@@ -12228,7 +12462,7 @@
         <v>44167</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:18">
+    <row r="169" spans="1:18">
       <c r="A169" s="23"/>
       <c r="B169" s="11">
         <f t="shared" si="3"/>
@@ -12277,7 +12511,7 @@
         <v>44181</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:18">
+    <row r="170" spans="1:18">
       <c r="A170" s="23"/>
       <c r="B170" s="11">
         <f t="shared" si="3"/>
@@ -12330,7 +12564,7 @@
         <v>44200</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:18">
+    <row r="171" spans="1:18">
       <c r="A171" s="23"/>
       <c r="B171" s="11">
         <f t="shared" si="3"/>
@@ -12383,7 +12617,7 @@
         <v>44207</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:18">
+    <row r="172" spans="1:18">
       <c r="A172" s="23"/>
       <c r="B172" s="11">
         <f t="shared" si="3"/>
@@ -12436,7 +12670,7 @@
         <v>44214</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:18">
+    <row r="173" spans="1:18">
       <c r="A173" s="23"/>
       <c r="B173" s="11">
         <f t="shared" si="3"/>
@@ -12483,7 +12717,7 @@
         <v>44221</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:18">
+    <row r="174" spans="1:18">
       <c r="A174" s="23"/>
       <c r="B174" s="11">
         <f t="shared" si="3"/>
@@ -12532,7 +12766,7 @@
         <v>44225</v>
       </c>
     </row>
-    <row r="175" ht="22.5" hidden="1" spans="1:18">
+    <row r="175" ht="22.5" spans="1:18">
       <c r="A175" s="23"/>
       <c r="B175" s="11">
         <f t="shared" si="3"/>
@@ -12581,7 +12815,7 @@
         <v>44246</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:18">
+    <row r="176" spans="1:18">
       <c r="A176" s="24"/>
       <c r="B176" s="11">
         <f t="shared" si="3"/>
@@ -12634,7 +12868,7 @@
         <v>44256</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:18">
+    <row r="177" spans="1:18">
       <c r="A177" s="23"/>
       <c r="B177" s="11">
         <f t="shared" si="3"/>
@@ -12683,7 +12917,7 @@
         <v>44265</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:18">
+    <row r="178" spans="1:18">
       <c r="A178" s="23"/>
       <c r="B178" s="11">
         <f t="shared" si="3"/>
@@ -12732,7 +12966,7 @@
         <v>44270</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:18">
+    <row r="179" spans="1:18">
       <c r="A179" s="23"/>
       <c r="B179" s="11">
         <f t="shared" si="3"/>
@@ -12785,7 +13019,7 @@
         <v>44277</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:18">
+    <row r="180" spans="1:18">
       <c r="A180" s="23"/>
       <c r="B180" s="11">
         <f t="shared" si="3"/>
@@ -12836,7 +13070,7 @@
         <v>44284</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:18">
+    <row r="181" spans="1:18">
       <c r="A181" s="23"/>
       <c r="B181" s="11">
         <f t="shared" si="3"/>
@@ -12887,7 +13121,7 @@
         <v>44298</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="1:18">
+    <row r="182" spans="1:18">
       <c r="A182" s="23"/>
       <c r="B182" s="11">
         <f t="shared" si="3"/>
@@ -12936,7 +13170,7 @@
         <v>44298</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:18">
+    <row r="183" spans="1:18">
       <c r="A183" s="23"/>
       <c r="B183" s="11">
         <f t="shared" si="3"/>
@@ -12983,7 +13217,7 @@
         <v>44305</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:18">
+    <row r="184" spans="1:18">
       <c r="A184" s="23"/>
       <c r="B184" s="11">
         <f t="shared" si="3"/>
@@ -13032,7 +13266,7 @@
         <v>44307</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:18">
+    <row r="185" spans="1:18">
       <c r="A185" s="23"/>
       <c r="B185" s="11">
         <f t="shared" si="3"/>
@@ -13087,7 +13321,7 @@
         <v>44312</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:18">
+    <row r="186" spans="1:18">
       <c r="A186" s="23"/>
       <c r="B186" s="11">
         <f t="shared" si="3"/>
@@ -13136,7 +13370,7 @@
         <v>44314</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:18">
+    <row r="187" spans="1:18">
       <c r="A187" s="23"/>
       <c r="B187" s="11">
         <f t="shared" si="3"/>
@@ -13185,7 +13419,7 @@
         <v>44322</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:18">
+    <row r="188" spans="1:18">
       <c r="A188" s="23"/>
       <c r="B188" s="11">
         <f t="shared" si="3"/>
@@ -13238,7 +13472,7 @@
         <v>44326</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:18">
+    <row r="189" spans="1:18">
       <c r="A189" s="23"/>
       <c r="B189" s="11">
         <f t="shared" si="3"/>
@@ -13291,7 +13525,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:18">
+    <row r="190" spans="1:18">
       <c r="A190" s="23"/>
       <c r="B190" s="11">
         <f t="shared" si="3"/>
@@ -13340,7 +13574,7 @@
         <v>44333</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:18">
+    <row r="191" spans="1:18">
       <c r="A191" s="23"/>
       <c r="B191" s="11">
         <f t="shared" si="3"/>
@@ -13389,7 +13623,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="192" hidden="1" spans="1:18">
+    <row r="192" spans="1:18">
       <c r="A192" s="23"/>
       <c r="B192" s="11">
         <f t="shared" si="3"/>
@@ -13438,7 +13672,7 @@
         <v>44333</v>
       </c>
     </row>
-    <row r="193" hidden="1" spans="1:18">
+    <row r="193" spans="1:18">
       <c r="A193" s="23"/>
       <c r="B193" s="11">
         <f t="shared" si="3"/>
@@ -13487,7 +13721,7 @@
         <v>44330</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:18">
+    <row r="194" spans="1:18">
       <c r="A194" s="23"/>
       <c r="B194" s="11">
         <f t="shared" si="3"/>
@@ -13536,7 +13770,7 @@
         <v>44340</v>
       </c>
     </row>
-    <row r="195" hidden="1" spans="1:18">
+    <row r="195" spans="1:18">
       <c r="A195" s="23"/>
       <c r="B195" s="11">
         <f t="shared" si="3"/>
@@ -13585,7 +13819,7 @@
         <v>44342</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:18">
+    <row r="196" spans="1:18">
       <c r="A196" s="23"/>
       <c r="B196" s="11">
         <f t="shared" si="3"/>
@@ -13634,7 +13868,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:18">
+    <row r="197" spans="1:18">
       <c r="A197" s="23"/>
       <c r="B197" s="11">
         <f t="shared" si="3"/>
@@ -13689,7 +13923,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:18">
+    <row r="198" spans="1:18">
       <c r="A198" s="30"/>
       <c r="B198" s="11">
         <f t="shared" si="3"/>
@@ -13738,7 +13972,7 @@
         <v>44351</v>
       </c>
     </row>
-    <row r="199" hidden="1" spans="1:18">
+    <row r="199" spans="1:18">
       <c r="A199" s="23"/>
       <c r="B199" s="11">
         <f t="shared" si="3"/>
@@ -13787,7 +14021,7 @@
         <v>44362</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:18">
+    <row r="200" spans="1:18">
       <c r="A200" s="23"/>
       <c r="B200" s="11">
         <f t="shared" si="3"/>
@@ -13836,7 +14070,7 @@
         <v>44362</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:18">
+    <row r="201" spans="1:18">
       <c r="A201" s="23"/>
       <c r="B201" s="11">
         <f t="shared" si="3"/>
@@ -13891,7 +14125,7 @@
         <v>44368</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:18">
+    <row r="202" spans="1:18">
       <c r="A202" s="23"/>
       <c r="B202" s="11">
         <f t="shared" si="3"/>
@@ -13940,7 +14174,7 @@
         <v>44368</v>
       </c>
     </row>
-    <row r="203" hidden="1" spans="1:18">
+    <row r="203" spans="1:18">
       <c r="A203" s="23"/>
       <c r="B203" s="11">
         <f t="shared" si="3"/>
@@ -13989,7 +14223,7 @@
         <v>44375</v>
       </c>
     </row>
-    <row r="204" hidden="1" spans="1:18">
+    <row r="204" spans="1:18">
       <c r="A204" s="23"/>
       <c r="B204" s="11">
         <f t="shared" si="3"/>
@@ -14038,7 +14272,7 @@
         <v>44377</v>
       </c>
     </row>
-    <row r="205" hidden="1" spans="1:18">
+    <row r="205" spans="1:18">
       <c r="A205" s="23"/>
       <c r="B205" s="11">
         <f t="shared" si="3"/>
@@ -14087,7 +14321,7 @@
         <v>44382</v>
       </c>
     </row>
-    <row r="206" hidden="1" spans="1:18">
+    <row r="206" spans="1:18">
       <c r="A206" s="34"/>
       <c r="B206" s="11">
         <f t="shared" si="3"/>
@@ -14134,7 +14368,7 @@
         <v>44382</v>
       </c>
     </row>
-    <row r="207" hidden="1" spans="1:18">
+    <row r="207" spans="1:18">
       <c r="A207" s="23"/>
       <c r="B207" s="11">
         <f t="shared" si="3"/>
@@ -14181,7 +14415,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="208" hidden="1" spans="1:18">
+    <row r="208" spans="1:18">
       <c r="A208" s="23"/>
       <c r="B208" s="11">
         <f t="shared" si="3"/>
@@ -14230,7 +14464,7 @@
         <v>44405</v>
       </c>
     </row>
-    <row r="209" hidden="1" spans="1:18">
+    <row r="209" spans="1:18">
       <c r="A209" s="23"/>
       <c r="B209" s="11">
         <f t="shared" si="3"/>
@@ -14277,7 +14511,7 @@
         <v>44405</v>
       </c>
     </row>
-    <row r="210" hidden="1" spans="1:18">
+    <row r="210" spans="1:18">
       <c r="A210" s="23"/>
       <c r="B210" s="11">
         <f t="shared" si="3"/>
@@ -14332,7 +14566,7 @@
         <v>44410</v>
       </c>
     </row>
-    <row r="211" hidden="1" spans="1:18">
+    <row r="211" spans="1:18">
       <c r="A211" s="23"/>
       <c r="B211" s="11">
         <f t="shared" si="3"/>
@@ -14381,7 +14615,7 @@
         <v>44421</v>
       </c>
     </row>
-    <row r="212" hidden="1" spans="1:18">
+    <row r="212" spans="1:18">
       <c r="A212" s="23"/>
       <c r="B212" s="11">
         <f t="shared" si="3"/>
@@ -14436,7 +14670,7 @@
         <v>44424</v>
       </c>
     </row>
-    <row r="213" hidden="1" spans="1:18">
+    <row r="213" spans="1:18">
       <c r="A213" s="23"/>
       <c r="B213" s="11">
         <f t="shared" si="3"/>
@@ -14489,7 +14723,7 @@
         <v>44424</v>
       </c>
     </row>
-    <row r="214" hidden="1" spans="1:18">
+    <row r="214" spans="1:18">
       <c r="A214" s="23"/>
       <c r="B214" s="11">
         <f t="shared" si="3"/>
@@ -14538,7 +14772,7 @@
         <v>44426</v>
       </c>
     </row>
-    <row r="215" hidden="1" spans="1:18">
+    <row r="215" spans="1:18">
       <c r="A215" s="23"/>
       <c r="B215" s="11">
         <f t="shared" si="3"/>
@@ -14587,7 +14821,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="216" hidden="1" spans="1:18">
+    <row r="216" spans="1:18">
       <c r="A216" s="23"/>
       <c r="B216" s="11">
         <f t="shared" si="3"/>
@@ -14640,7 +14874,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="217" hidden="1" spans="1:18">
+    <row r="217" spans="1:18">
       <c r="A217" s="23"/>
       <c r="B217" s="11">
         <f>ROW()-1</f>
@@ -14687,7 +14921,7 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="218" hidden="1" spans="1:18">
+    <row r="218" spans="1:18">
       <c r="A218" s="23"/>
       <c r="B218" s="11">
         <f t="shared" ref="B218:B252" si="4">ROW()-1</f>
@@ -14742,7 +14976,7 @@
         <v>44440</v>
       </c>
     </row>
-    <row r="219" hidden="1" spans="1:18">
+    <row r="219" spans="1:18">
       <c r="A219" s="23"/>
       <c r="B219" s="11">
         <f t="shared" si="4"/>
@@ -14791,7 +15025,7 @@
         <v>44445</v>
       </c>
     </row>
-    <row r="220" hidden="1" spans="1:18">
+    <row r="220" spans="1:18">
       <c r="A220" s="23"/>
       <c r="B220" s="11">
         <f t="shared" si="4"/>
@@ -14840,7 +15074,7 @@
         <v>44446</v>
       </c>
     </row>
-    <row r="221" ht="22.5" hidden="1" spans="1:18">
+    <row r="221" ht="22.5" spans="1:18">
       <c r="A221" s="23"/>
       <c r="B221" s="11">
         <f t="shared" si="4"/>
@@ -14889,7 +15123,7 @@
         <v>44447</v>
       </c>
     </row>
-    <row r="222" hidden="1" spans="1:18">
+    <row r="222" spans="1:18">
       <c r="A222" s="36"/>
       <c r="B222" s="11">
         <f t="shared" si="4"/>
@@ -14938,7 +15172,7 @@
         <v>44449</v>
       </c>
     </row>
-    <row r="223" hidden="1" spans="1:18">
+    <row r="223" spans="1:18">
       <c r="A223" s="36"/>
       <c r="B223" s="11">
         <f t="shared" si="4"/>
@@ -14985,7 +15219,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="224" hidden="1" spans="1:18">
+    <row r="224" spans="1:18">
       <c r="A224" s="36"/>
       <c r="B224" s="11">
         <f t="shared" si="4"/>
@@ -15034,7 +15268,7 @@
         <v>44463</v>
       </c>
     </row>
-    <row r="225" hidden="1" spans="1:18">
+    <row r="225" spans="1:18">
       <c r="A225" s="36"/>
       <c r="B225" s="11">
         <f t="shared" si="4"/>
@@ -15087,7 +15321,7 @@
         <v>44467</v>
       </c>
     </row>
-    <row r="226" hidden="1" spans="1:18">
+    <row r="226" spans="1:18">
       <c r="A226" s="23"/>
       <c r="B226" s="11">
         <f t="shared" si="4"/>
@@ -15140,7 +15374,7 @@
         <v>44489</v>
       </c>
     </row>
-    <row r="227" hidden="1" spans="1:18">
+    <row r="227" spans="1:18">
       <c r="A227" s="38"/>
       <c r="B227" s="11">
         <f t="shared" si="4"/>
@@ -15189,7 +15423,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="228" hidden="1" spans="1:18">
+    <row r="228" spans="1:18">
       <c r="A228" s="39" t="s">
         <v>465</v>
       </c>
@@ -15246,7 +15480,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="229" hidden="1" spans="1:18">
+    <row r="229" spans="1:18">
       <c r="A229" s="30"/>
       <c r="B229" s="11">
         <f t="shared" si="4"/>
@@ -15295,7 +15529,7 @@
         <v>44524</v>
       </c>
     </row>
-    <row r="230" hidden="1" spans="1:18">
+    <row r="230" spans="1:18">
       <c r="A230" s="41"/>
       <c r="B230" s="11">
         <f t="shared" si="4"/>
@@ -15346,7 +15580,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="231" hidden="1" spans="1:18">
+    <row r="231" spans="1:18">
       <c r="A231" s="41"/>
       <c r="B231" s="11">
         <f t="shared" si="4"/>
@@ -15401,7 +15635,7 @@
         <v>44543</v>
       </c>
     </row>
-    <row r="232" hidden="1" spans="1:18">
+    <row r="232" spans="1:18">
       <c r="A232" s="23"/>
       <c r="B232" s="11">
         <f t="shared" si="4"/>
@@ -15456,7 +15690,7 @@
         <v>44544</v>
       </c>
     </row>
-    <row r="233" hidden="1" spans="1:18">
+    <row r="233" spans="1:18">
       <c r="A233" s="41"/>
       <c r="B233" s="11">
         <f t="shared" si="4"/>
@@ -15505,7 +15739,7 @@
         <v>44545</v>
       </c>
     </row>
-    <row r="234" hidden="1" spans="1:18">
+    <row r="234" spans="1:18">
       <c r="A234" s="41"/>
       <c r="B234" s="11">
         <f t="shared" si="4"/>
@@ -15554,7 +15788,7 @@
         <v>44557</v>
       </c>
     </row>
-    <row r="235" hidden="1" spans="1:18">
+    <row r="235" spans="1:18">
       <c r="A235" s="30"/>
       <c r="B235" s="11">
         <f t="shared" si="4"/>
@@ -15603,7 +15837,7 @@
         <v>44574</v>
       </c>
     </row>
-    <row r="236" hidden="1" spans="1:18">
+    <row r="236" spans="1:18">
       <c r="A236" s="41"/>
       <c r="B236" s="11">
         <f t="shared" si="4"/>
@@ -15654,7 +15888,7 @@
         <v>44602</v>
       </c>
     </row>
-    <row r="237" hidden="1" spans="1:18">
+    <row r="237" spans="1:18">
       <c r="A237" s="23"/>
       <c r="B237" s="11">
         <f t="shared" si="4"/>
@@ -15707,7 +15941,7 @@
         <v>44613</v>
       </c>
     </row>
-    <row r="238" hidden="1" spans="1:18">
+    <row r="238" spans="1:18">
       <c r="A238" s="41"/>
       <c r="B238" s="11">
         <f t="shared" si="4"/>
@@ -15756,7 +15990,7 @@
         <v>44620</v>
       </c>
     </row>
-    <row r="239" hidden="1" spans="1:18">
+    <row r="239" spans="1:18">
       <c r="A239" s="20"/>
       <c r="B239" s="11">
         <f t="shared" si="4"/>
@@ -15811,7 +16045,7 @@
         <v>44622</v>
       </c>
     </row>
-    <row r="240" hidden="1" spans="1:18">
+    <row r="240" spans="1:18">
       <c r="A240" s="23"/>
       <c r="B240" s="11">
         <f t="shared" si="4"/>
@@ -15866,7 +16100,7 @@
         <v>44627</v>
       </c>
     </row>
-    <row r="241" hidden="1" spans="1:18">
+    <row r="241" spans="1:18">
       <c r="A241" s="23"/>
       <c r="B241" s="11">
         <f t="shared" si="4"/>
@@ -15921,7 +16155,7 @@
         <v>44627</v>
       </c>
     </row>
-    <row r="242" hidden="1" spans="1:18">
+    <row r="242" spans="1:18">
       <c r="A242" s="41"/>
       <c r="B242" s="11">
         <f t="shared" si="4"/>
@@ -15970,7 +16204,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="243" hidden="1" spans="1:18">
+    <row r="243" spans="1:18">
       <c r="A243" s="24"/>
       <c r="B243" s="11">
         <f t="shared" si="4"/>
@@ -16023,7 +16257,7 @@
         <v>44648</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:18">
+    <row r="244" spans="1:18">
       <c r="A244" s="20"/>
       <c r="B244" s="11">
         <f t="shared" si="4"/>
@@ -16070,7 +16304,7 @@
         <v>44648</v>
       </c>
     </row>
-    <row r="245" hidden="1" spans="1:18">
+    <row r="245" spans="1:18">
       <c r="A245" s="20"/>
       <c r="B245" s="11">
         <f t="shared" si="4"/>
@@ -16119,7 +16353,7 @@
         <v>44648</v>
       </c>
     </row>
-    <row r="246" hidden="1" spans="1:18">
+    <row r="246" spans="1:18">
       <c r="A246" s="20"/>
       <c r="B246" s="11">
         <f t="shared" si="4"/>
@@ -16168,7 +16402,7 @@
         <v>44650</v>
       </c>
     </row>
-    <row r="247" hidden="1" spans="1:18">
+    <row r="247" spans="1:18">
       <c r="A247" s="20"/>
       <c r="B247" s="11">
         <f t="shared" si="4"/>
@@ -16219,7 +16453,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="248" hidden="1" spans="1:18">
+    <row r="248" spans="1:18">
       <c r="A248" s="23"/>
       <c r="B248" s="11">
         <f t="shared" si="4"/>
@@ -16274,7 +16508,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="249" hidden="1" spans="1:18">
+    <row r="249" spans="1:18">
       <c r="A249" s="23"/>
       <c r="B249" s="11">
         <f t="shared" si="4"/>
@@ -16329,7 +16563,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="250" hidden="1" spans="1:18">
+    <row r="250" spans="1:18">
       <c r="A250" s="38"/>
       <c r="B250" s="11">
         <f t="shared" si="4"/>
@@ -16378,7 +16612,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="251" hidden="1" spans="1:18">
+    <row r="251" spans="1:18">
       <c r="A251" s="38"/>
       <c r="B251" s="11">
         <f t="shared" si="4"/>
@@ -16433,7 +16667,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="252" hidden="1" spans="1:18">
+    <row r="252" spans="1:18">
       <c r="A252" s="38"/>
       <c r="B252" s="11">
         <f t="shared" si="4"/>
@@ -16480,7 +16714,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:18">
+    <row r="253" spans="1:18">
       <c r="A253" s="38"/>
       <c r="B253" s="11">
         <f t="shared" ref="B253:B316" si="5">ROW()-1</f>
@@ -16529,7 +16763,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="254" hidden="1" spans="1:18">
+    <row r="254" spans="1:18">
       <c r="A254" s="20"/>
       <c r="B254" s="11">
         <f t="shared" si="5"/>
@@ -16578,7 +16812,7 @@
         <v>44704</v>
       </c>
     </row>
-    <row r="255" hidden="1" spans="1:18">
+    <row r="255" spans="1:18">
       <c r="A255" s="20"/>
       <c r="B255" s="11">
         <f t="shared" si="5"/>
@@ -16633,7 +16867,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="256" hidden="1" spans="1:18">
+    <row r="256" spans="1:18">
       <c r="A256" s="20"/>
       <c r="B256" s="11">
         <f t="shared" si="5"/>
@@ -16682,7 +16916,7 @@
         <v>44718</v>
       </c>
     </row>
-    <row r="257" hidden="1" spans="1:18">
+    <row r="257" spans="1:18">
       <c r="A257" s="44" t="s">
         <v>501</v>
       </c>
@@ -16737,7 +16971,7 @@
         <v>44725</v>
       </c>
     </row>
-    <row r="258" hidden="1" spans="1:18">
+    <row r="258" spans="1:18">
       <c r="A258" s="20"/>
       <c r="B258" s="11">
         <f t="shared" si="5"/>
@@ -16786,7 +17020,7 @@
         <v>44727</v>
       </c>
     </row>
-    <row r="259" ht="22.5" hidden="1" spans="1:18">
+    <row r="259" ht="22.5" spans="1:18">
       <c r="A259" s="20"/>
       <c r="B259" s="11">
         <f t="shared" si="5"/>
@@ -16835,7 +17069,7 @@
         <v>44732</v>
       </c>
     </row>
-    <row r="260" hidden="1" spans="1:18">
+    <row r="260" spans="1:18">
       <c r="A260" s="20"/>
       <c r="B260" s="11">
         <f t="shared" si="5"/>
@@ -16890,7 +17124,7 @@
         <v>44739</v>
       </c>
     </row>
-    <row r="261" hidden="1" spans="1:18">
+    <row r="261" spans="1:18">
       <c r="A261" s="44" t="s">
         <v>509</v>
       </c>
@@ -16945,7 +17179,7 @@
         <v>44741</v>
       </c>
     </row>
-    <row r="262" hidden="1" spans="1:18">
+    <row r="262" spans="1:18">
       <c r="A262" s="20"/>
       <c r="B262" s="11">
         <f t="shared" si="5"/>
@@ -16998,7 +17232,7 @@
         <v>44741</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:18">
+    <row r="263" spans="1:18">
       <c r="A263" s="20"/>
       <c r="B263" s="11">
         <f t="shared" si="5"/>
@@ -17045,7 +17279,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="264" hidden="1" spans="1:18">
+    <row r="264" spans="1:18">
       <c r="A264" s="23"/>
       <c r="B264" s="11">
         <f t="shared" si="5"/>
@@ -17098,7 +17332,7 @@
         <v>44748</v>
       </c>
     </row>
-    <row r="265" hidden="1" spans="1:18">
+    <row r="265" spans="1:18">
       <c r="A265" s="20"/>
       <c r="B265" s="11">
         <f t="shared" si="5"/>
@@ -17149,7 +17383,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="266" hidden="1" spans="1:18">
+    <row r="266" spans="1:18">
       <c r="A266" s="20"/>
       <c r="B266" s="11">
         <f t="shared" si="5"/>
@@ -17198,7 +17432,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="267" hidden="1" spans="1:18">
+    <row r="267" spans="1:18">
       <c r="A267" s="23"/>
       <c r="B267" s="11">
         <f t="shared" si="5"/>
@@ -17251,7 +17485,7 @@
         <v>44753</v>
       </c>
     </row>
-    <row r="268" hidden="1" spans="1:18">
+    <row r="268" spans="1:18">
       <c r="A268" s="20"/>
       <c r="B268" s="11">
         <f t="shared" si="5"/>
@@ -17300,7 +17534,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="269" hidden="1" spans="1:18">
+    <row r="269" spans="1:18">
       <c r="A269" s="20"/>
       <c r="B269" s="11">
         <f t="shared" si="5"/>
@@ -17353,7 +17587,7 @@
         <v>44767</v>
       </c>
     </row>
-    <row r="270" hidden="1" spans="1:18">
+    <row r="270" spans="1:18">
       <c r="A270" s="20"/>
       <c r="B270" s="11">
         <f t="shared" si="5"/>
@@ -17408,7 +17642,7 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="271" hidden="1" spans="1:18">
+    <row r="271" spans="1:18">
       <c r="A271" s="20"/>
       <c r="B271" s="11">
         <f t="shared" si="5"/>
@@ -17463,7 +17697,7 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="272" hidden="1" spans="1:18">
+    <row r="272" spans="1:18">
       <c r="A272" s="20"/>
       <c r="B272" s="11">
         <f t="shared" si="5"/>
@@ -17510,7 +17744,7 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="273" hidden="1" spans="1:18">
+    <row r="273" spans="1:18">
       <c r="A273" s="20"/>
       <c r="B273" s="11">
         <f t="shared" si="5"/>
@@ -17561,7 +17795,7 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:18">
+    <row r="274" spans="1:18">
       <c r="A274" s="20"/>
       <c r="B274" s="11">
         <f t="shared" si="5"/>
@@ -17610,7 +17844,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="275" hidden="1" spans="1:18">
+    <row r="275" spans="1:18">
       <c r="A275" s="20"/>
       <c r="B275" s="11">
         <f t="shared" si="5"/>
@@ -17665,7 +17899,7 @@
         <v>44788</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:18">
+    <row r="276" spans="1:18">
       <c r="A276" s="20"/>
       <c r="B276" s="11">
         <f t="shared" si="5"/>
@@ -17714,7 +17948,7 @@
         <v>44809</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:18">
+    <row r="277" spans="1:18">
       <c r="A277" s="23"/>
       <c r="B277" s="11">
         <f t="shared" si="5"/>
@@ -17769,7 +18003,7 @@
         <v>44809</v>
       </c>
     </row>
-    <row r="278" hidden="1" spans="1:18">
+    <row r="278" spans="1:18">
       <c r="A278" s="20"/>
       <c r="B278" s="11">
         <f t="shared" si="5"/>
@@ -17814,7 +18048,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="279" hidden="1" spans="1:18">
+    <row r="279" spans="1:18">
       <c r="A279" s="20"/>
       <c r="B279" s="11">
         <f t="shared" si="5"/>
@@ -17867,7 +18101,7 @@
         <v>44823</v>
       </c>
     </row>
-    <row r="280" hidden="1" spans="1:18">
+    <row r="280" spans="1:18">
       <c r="A280" s="20"/>
       <c r="B280" s="11">
         <f t="shared" si="5"/>
@@ -17918,7 +18152,7 @@
         <v>44844</v>
       </c>
     </row>
-    <row r="281" hidden="1" spans="1:18">
+    <row r="281" spans="1:18">
       <c r="A281" s="20"/>
       <c r="B281" s="11">
         <f t="shared" si="5"/>
@@ -17967,7 +18201,7 @@
         <v>44851</v>
       </c>
     </row>
-    <row r="282" hidden="1" spans="1:18">
+    <row r="282" spans="1:18">
       <c r="A282" s="20"/>
       <c r="B282" s="11">
         <f t="shared" si="5"/>
@@ -18016,7 +18250,7 @@
         <v>44865</v>
       </c>
     </row>
-    <row r="283" hidden="1" spans="1:18">
+    <row r="283" spans="1:18">
       <c r="A283" s="20"/>
       <c r="B283" s="11">
         <f t="shared" si="5"/>
@@ -18069,7 +18303,7 @@
         <v>44867</v>
       </c>
     </row>
-    <row r="284" hidden="1" spans="1:18">
+    <row r="284" spans="1:18">
       <c r="A284" s="20"/>
       <c r="B284" s="11">
         <f t="shared" si="5"/>
@@ -18124,7 +18358,7 @@
         <v>44888</v>
       </c>
     </row>
-    <row r="285" hidden="1" spans="1:18">
+    <row r="285" spans="1:18">
       <c r="A285" s="23"/>
       <c r="B285" s="11">
         <f t="shared" si="5"/>
@@ -18177,7 +18411,7 @@
         <v>44972</v>
       </c>
     </row>
-    <row r="286" hidden="1" spans="1:18">
+    <row r="286" spans="1:18">
       <c r="A286" s="20"/>
       <c r="B286" s="11">
         <f t="shared" si="5"/>
@@ -18226,7 +18460,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="287" hidden="1" spans="1:18">
+    <row r="287" spans="1:18">
       <c r="A287" s="23"/>
       <c r="B287" s="11">
         <f t="shared" si="5"/>
@@ -18279,7 +18513,7 @@
         <v>44977</v>
       </c>
     </row>
-    <row r="288" hidden="1" spans="1:18">
+    <row r="288" spans="1:18">
       <c r="A288" s="20"/>
       <c r="B288" s="11">
         <f t="shared" si="5"/>
@@ -18328,7 +18562,7 @@
         <v>44979</v>
       </c>
     </row>
-    <row r="289" hidden="1" spans="1:18">
+    <row r="289" spans="1:18">
       <c r="A289" s="23"/>
       <c r="B289" s="11">
         <f t="shared" si="5"/>
@@ -18381,7 +18615,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="290" hidden="1" spans="1:18">
+    <row r="290" spans="1:18">
       <c r="A290" s="20"/>
       <c r="B290" s="11">
         <f t="shared" si="5"/>
@@ -18434,7 +18668,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="291" hidden="1" spans="1:18">
+    <row r="291" spans="1:18">
       <c r="A291" s="23"/>
       <c r="B291" s="11">
         <f t="shared" si="5"/>
@@ -18487,7 +18721,7 @@
         <v>45026</v>
       </c>
     </row>
-    <row r="292" hidden="1" spans="1:18">
+    <row r="292" spans="1:18">
       <c r="A292" s="20"/>
       <c r="B292" s="11">
         <f t="shared" si="5"/>
@@ -18536,7 +18770,7 @@
         <v>45026</v>
       </c>
     </row>
-    <row r="293" hidden="1" spans="1:18">
+    <row r="293" spans="1:18">
       <c r="A293" s="20"/>
       <c r="B293" s="11">
         <f t="shared" si="5"/>
@@ -18585,7 +18819,7 @@
         <v>45028</v>
       </c>
     </row>
-    <row r="294" hidden="1" spans="1:18">
+    <row r="294" spans="1:18">
       <c r="A294" s="20"/>
       <c r="B294" s="11">
         <f t="shared" si="5"/>
@@ -18634,7 +18868,7 @@
         <v>45033</v>
       </c>
     </row>
-    <row r="295" hidden="1" spans="1:18">
+    <row r="295" spans="1:18">
       <c r="A295" s="20"/>
       <c r="B295" s="11">
         <f t="shared" si="5"/>
@@ -18687,7 +18921,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="296" hidden="1" spans="1:18">
+    <row r="296" spans="1:18">
       <c r="A296" s="20"/>
       <c r="B296" s="11">
         <f t="shared" si="5"/>
@@ -18736,7 +18970,7 @@
         <v>45040</v>
       </c>
     </row>
-    <row r="297" hidden="1" spans="1:18">
+    <row r="297" spans="1:18">
       <c r="A297" s="23"/>
       <c r="B297" s="11">
         <f t="shared" si="5"/>
@@ -18789,7 +19023,7 @@
         <v>45040</v>
       </c>
     </row>
-    <row r="298" hidden="1" spans="1:18">
+    <row r="298" spans="1:18">
       <c r="A298" s="20"/>
       <c r="B298" s="11">
         <f t="shared" si="5"/>
@@ -18838,7 +19072,7 @@
         <v>45042</v>
       </c>
     </row>
-    <row r="299" hidden="1" spans="1:18">
+    <row r="299" spans="1:18">
       <c r="A299" s="20"/>
       <c r="B299" s="11">
         <f t="shared" si="5"/>
@@ -18887,7 +19121,7 @@
         <v>45061</v>
       </c>
     </row>
-    <row r="300" hidden="1" spans="1:18">
+    <row r="300" spans="1:18">
       <c r="A300" s="20"/>
       <c r="B300" s="11">
         <f t="shared" si="5"/>
@@ -18936,7 +19170,7 @@
         <v>45075</v>
       </c>
     </row>
-    <row r="301" hidden="1" spans="1:18">
+    <row r="301" spans="1:18">
       <c r="A301" s="20"/>
       <c r="B301" s="11">
         <f t="shared" si="5"/>
@@ -18983,7 +19217,7 @@
         <v>45077</v>
       </c>
     </row>
-    <row r="302" hidden="1" spans="1:18">
+    <row r="302" spans="1:18">
       <c r="A302" s="20"/>
       <c r="B302" s="11">
         <f t="shared" si="5"/>
@@ -19036,7 +19270,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="303" hidden="1" spans="1:18">
+    <row r="303" spans="1:18">
       <c r="A303" s="23"/>
       <c r="B303" s="11">
         <f t="shared" si="5"/>
@@ -19089,7 +19323,7 @@
         <v>45084</v>
       </c>
     </row>
-    <row r="304" hidden="1" spans="1:18">
+    <row r="304" spans="1:18">
       <c r="A304" s="20"/>
       <c r="B304" s="11">
         <f t="shared" si="5"/>
@@ -19144,7 +19378,7 @@
         <v>45084</v>
       </c>
     </row>
-    <row r="305" hidden="1" spans="1:18">
+    <row r="305" spans="1:18">
       <c r="A305" s="20"/>
       <c r="B305" s="11">
         <f t="shared" si="5"/>
@@ -19193,7 +19427,7 @@
         <v>45089</v>
       </c>
     </row>
-    <row r="306" hidden="1" spans="1:18">
+    <row r="306" spans="1:18">
       <c r="A306" s="20"/>
       <c r="B306" s="11">
         <f t="shared" si="5"/>
@@ -19242,7 +19476,7 @@
         <v>45089</v>
       </c>
     </row>
-    <row r="307" hidden="1" spans="1:18">
+    <row r="307" spans="1:18">
       <c r="A307" s="20"/>
       <c r="B307" s="11">
         <f t="shared" si="5"/>
@@ -19291,7 +19525,7 @@
         <v>45096</v>
       </c>
     </row>
-    <row r="308" hidden="1" spans="1:18">
+    <row r="308" spans="1:18">
       <c r="A308" s="23"/>
       <c r="B308" s="11">
         <f t="shared" si="5"/>
@@ -19344,7 +19578,7 @@
         <v>45103</v>
       </c>
     </row>
-    <row r="309" hidden="1" spans="1:18">
+    <row r="309" spans="1:18">
       <c r="A309" s="23"/>
       <c r="B309" s="11">
         <f t="shared" si="5"/>
@@ -19393,7 +19627,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="310" hidden="1" spans="1:18">
+    <row r="310" spans="1:18">
       <c r="A310" s="23"/>
       <c r="B310" s="11">
         <f t="shared" si="5"/>
@@ -19442,7 +19676,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="311" hidden="1" spans="1:18">
+    <row r="311" spans="1:18">
       <c r="A311" s="23"/>
       <c r="B311" s="11">
         <f t="shared" si="5"/>
@@ -19491,7 +19725,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="312" hidden="1" spans="1:18">
+    <row r="312" spans="1:18">
       <c r="A312" s="23"/>
       <c r="B312" s="11">
         <f t="shared" si="5"/>
@@ -19536,7 +19770,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="313" hidden="1" spans="1:18">
+    <row r="313" spans="1:18">
       <c r="A313" s="23"/>
       <c r="B313" s="11">
         <f t="shared" si="5"/>
@@ -19585,7 +19819,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="314" hidden="1" spans="1:18">
+    <row r="314" spans="1:18">
       <c r="A314" s="23"/>
       <c r="B314" s="11">
         <f t="shared" si="5"/>
@@ -19634,7 +19868,7 @@
         <v>45161</v>
       </c>
     </row>
-    <row r="315" hidden="1" spans="1:18">
+    <row r="315" spans="1:18">
       <c r="A315" s="23"/>
       <c r="B315" s="11">
         <f t="shared" si="5"/>
@@ -19681,7 +19915,7 @@
         <v>45161</v>
       </c>
     </row>
-    <row r="316" hidden="1" spans="1:18">
+    <row r="316" spans="1:18">
       <c r="A316" s="23"/>
       <c r="B316" s="11">
         <f t="shared" si="5"/>
@@ -19730,7 +19964,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:18">
+    <row r="317" spans="1:18">
       <c r="A317" s="23"/>
       <c r="B317" s="11">
         <f t="shared" ref="B317:B380" si="6">ROW()-1</f>
@@ -19777,7 +20011,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:18">
+    <row r="318" spans="1:18">
       <c r="A318" s="23"/>
       <c r="B318" s="11">
         <f t="shared" si="6"/>
@@ -19824,7 +20058,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:18">
+    <row r="319" spans="1:18">
       <c r="A319" s="23"/>
       <c r="B319" s="11">
         <f t="shared" si="6"/>
@@ -19877,7 +20111,7 @@
         <v>45229</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:18">
+    <row r="320" spans="1:18">
       <c r="A320" s="23"/>
       <c r="B320" s="11">
         <f t="shared" si="6"/>
@@ -19930,7 +20164,7 @@
         <v>45229</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:18">
+    <row r="321" spans="1:18">
       <c r="A321" s="23"/>
       <c r="B321" s="11">
         <f t="shared" si="6"/>
@@ -19983,7 +20217,7 @@
         <v>45229</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:18">
+    <row r="322" spans="1:18">
       <c r="A322" s="23"/>
       <c r="B322" s="11">
         <f t="shared" si="6"/>
@@ -20036,7 +20270,7 @@
         <v>45243</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:18">
+    <row r="323" spans="1:18">
       <c r="A323" s="23"/>
       <c r="B323" s="11">
         <f t="shared" si="6"/>
@@ -20085,7 +20319,7 @@
         <v>45245</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:18">
+    <row r="324" spans="1:18">
       <c r="A324" s="23"/>
       <c r="B324" s="11">
         <f t="shared" si="6"/>
@@ -20140,7 +20374,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:18">
+    <row r="325" spans="1:18">
       <c r="A325" s="23"/>
       <c r="B325" s="11">
         <f t="shared" si="6"/>
@@ -20189,7 +20423,7 @@
         <v>45266</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:18">
+    <row r="326" spans="1:18">
       <c r="A326" s="23"/>
       <c r="B326" s="11">
         <f t="shared" si="6"/>
@@ -20242,7 +20476,7 @@
         <v>45271</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:18">
+    <row r="327" spans="1:18">
       <c r="A327" s="23"/>
       <c r="B327" s="11">
         <f t="shared" si="6"/>
@@ -20287,7 +20521,7 @@
         <v>45271</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:18">
+    <row r="328" spans="1:18">
       <c r="A328" s="23"/>
       <c r="B328" s="11">
         <f t="shared" si="6"/>
@@ -20334,7 +20568,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:18">
+    <row r="329" spans="1:18">
       <c r="A329" s="23"/>
       <c r="B329" s="11">
         <f t="shared" si="6"/>
@@ -20387,7 +20621,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:18">
+    <row r="330" spans="1:18">
       <c r="A330" s="23"/>
       <c r="B330" s="11">
         <f t="shared" si="6"/>
@@ -20440,7 +20674,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:18">
+    <row r="331" spans="1:18">
       <c r="A331" s="23"/>
       <c r="B331" s="11">
         <f t="shared" si="6"/>
@@ -20493,7 +20727,7 @@
         <v>45348</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:18">
+    <row r="332" spans="1:18">
       <c r="A332" s="23"/>
       <c r="B332" s="11">
         <f t="shared" si="6"/>
@@ -20546,7 +20780,7 @@
         <v>45348</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:18">
+    <row r="333" spans="1:18">
       <c r="A333" s="23"/>
       <c r="B333" s="11">
         <f t="shared" si="6"/>
@@ -20599,7 +20833,7 @@
         <v>45350</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:18">
+    <row r="334" spans="1:18">
       <c r="A334" s="23"/>
       <c r="B334" s="11">
         <f t="shared" si="6"/>
@@ -20652,7 +20886,7 @@
         <v>45355</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:18">
+    <row r="335" spans="1:18">
       <c r="A335" s="23"/>
       <c r="B335" s="11">
         <f t="shared" si="6"/>
@@ -20699,7 +20933,7 @@
         <v>45355</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:18">
+    <row r="336" spans="1:18">
       <c r="A336" s="23"/>
       <c r="B336" s="11">
         <f t="shared" si="6"/>
@@ -20752,7 +20986,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:18">
+    <row r="337" spans="1:18">
       <c r="A337" s="23"/>
       <c r="B337" s="11">
         <f t="shared" si="6"/>
@@ -20805,7 +21039,7 @@
         <v>45364</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:18">
+    <row r="338" spans="1:18">
       <c r="A338" s="23"/>
       <c r="B338" s="11">
         <f t="shared" si="6"/>
@@ -20854,7 +21088,7 @@
         <v>45371</v>
       </c>
     </row>
-    <row r="339" hidden="1" spans="1:18">
+    <row r="339" spans="1:18">
       <c r="A339" s="23"/>
       <c r="B339" s="11">
         <f t="shared" si="6"/>
@@ -20903,7 +21137,7 @@
         <v>45378</v>
       </c>
     </row>
-    <row r="340" hidden="1" spans="1:18">
+    <row r="340" spans="1:18">
       <c r="A340" s="23"/>
       <c r="B340" s="11">
         <f t="shared" si="6"/>
@@ -20950,7 +21184,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:18">
+    <row r="341" spans="1:18">
       <c r="A341" s="23"/>
       <c r="B341" s="11">
         <f t="shared" si="6"/>
@@ -20999,7 +21233,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:18">
+    <row r="342" spans="1:18">
       <c r="A342" s="23"/>
       <c r="B342" s="11">
         <f t="shared" si="6"/>
@@ -21048,7 +21282,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:18">
+    <row r="343" spans="1:18">
       <c r="A343" s="23"/>
       <c r="B343" s="11">
         <f t="shared" si="6"/>
@@ -21103,7 +21337,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:18">
+    <row r="344" spans="1:18">
       <c r="A344" s="23"/>
       <c r="B344" s="11">
         <f t="shared" si="6"/>
@@ -21158,7 +21392,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:18">
+    <row r="345" spans="1:18">
       <c r="A345" s="23"/>
       <c r="B345" s="11">
         <f t="shared" si="6"/>
@@ -21207,7 +21441,7 @@
         <v>45399</v>
       </c>
     </row>
-    <row r="346" hidden="1" spans="1:18">
+    <row r="346" spans="1:18">
       <c r="A346" s="23"/>
       <c r="B346" s="11">
         <f t="shared" si="6"/>
@@ -21256,7 +21490,7 @@
         <v>45404</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:18">
+    <row r="347" spans="1:18">
       <c r="A347" s="23"/>
       <c r="B347" s="11">
         <f t="shared" si="6"/>
@@ -21303,7 +21537,7 @@
         <v>45406</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:18">
+    <row r="348" spans="1:18">
       <c r="A348" s="23"/>
       <c r="B348" s="11">
         <f t="shared" si="6"/>
@@ -21352,7 +21586,7 @@
         <v>45410</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:18">
+    <row r="349" spans="1:18">
       <c r="A349" s="23"/>
       <c r="B349" s="11">
         <f t="shared" si="6"/>
@@ -21401,7 +21635,7 @@
         <v>45410</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:18">
+    <row r="350" spans="1:18">
       <c r="A350" s="23"/>
       <c r="B350" s="11">
         <f t="shared" si="6"/>
@@ -21454,7 +21688,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:18">
+    <row r="351" spans="1:18">
       <c r="A351" s="23"/>
       <c r="B351" s="11">
         <f t="shared" si="6"/>
@@ -21507,7 +21741,7 @@
         <v>45425</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:18">
+    <row r="352" spans="1:18">
       <c r="A352" s="23"/>
       <c r="B352" s="11">
         <f t="shared" si="6"/>
@@ -21562,7 +21796,7 @@
         <v>45425</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:18">
+    <row r="353" spans="1:18">
       <c r="A353" s="23"/>
       <c r="B353" s="11">
         <f t="shared" si="6"/>
@@ -21611,7 +21845,7 @@
         <v>45425</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:18">
+    <row r="354" spans="1:18">
       <c r="A354" s="23"/>
       <c r="B354" s="11">
         <f t="shared" si="6"/>
@@ -21660,7 +21894,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:18">
+    <row r="355" spans="1:18">
       <c r="A355" s="23" t="s">
         <v>621</v>
       </c>
@@ -21707,7 +21941,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:18">
+    <row r="356" spans="1:18">
       <c r="A356" s="23"/>
       <c r="B356" s="11">
         <f t="shared" si="6"/>
@@ -21756,7 +21990,7 @@
         <v>45439</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:18">
+    <row r="357" spans="1:18">
       <c r="A357" s="23"/>
       <c r="B357" s="11">
         <f t="shared" si="6"/>
@@ -21805,7 +22039,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:18">
+    <row r="358" spans="1:18">
       <c r="A358" s="23"/>
       <c r="B358" s="11">
         <f t="shared" si="6"/>
@@ -21854,7 +22088,7 @@
         <v>45448</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:18">
+    <row r="359" spans="1:18">
       <c r="A359" s="23"/>
       <c r="B359" s="11">
         <f t="shared" si="6"/>
@@ -21903,7 +22137,7 @@
         <v>45467</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:18">
+    <row r="360" spans="1:18">
       <c r="A360" s="23"/>
       <c r="B360" s="11">
         <f t="shared" si="6"/>
@@ -21952,7 +22186,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:18">
+    <row r="361" spans="1:18">
       <c r="A361" s="23"/>
       <c r="B361" s="11">
         <f t="shared" si="6"/>
@@ -22001,7 +22235,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:18">
+    <row r="362" spans="1:18">
       <c r="A362" s="23"/>
       <c r="B362" s="11">
         <f t="shared" si="6"/>
@@ -22050,7 +22284,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:18">
+    <row r="363" spans="1:18">
       <c r="A363" s="23"/>
       <c r="B363" s="11">
         <f t="shared" si="6"/>
@@ -22103,7 +22337,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:18">
+    <row r="364" spans="1:18">
       <c r="A364" s="23"/>
       <c r="B364" s="11">
         <f t="shared" si="6"/>
@@ -22158,7 +22392,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:18">
+    <row r="365" spans="1:18">
       <c r="A365" s="23"/>
       <c r="B365" s="11">
         <f t="shared" si="6"/>
@@ -22207,7 +22441,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:18">
+    <row r="366" spans="1:18">
       <c r="A366" s="23"/>
       <c r="B366" s="11">
         <f t="shared" si="6"/>
@@ -22260,7 +22494,7 @@
         <v>45481</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:18">
+    <row r="367" spans="1:18">
       <c r="A367" s="23"/>
       <c r="B367" s="11">
         <f t="shared" si="6"/>
@@ -22309,7 +22543,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:18">
+    <row r="368" spans="1:18">
       <c r="A368" s="23"/>
       <c r="B368" s="11">
         <f t="shared" si="6"/>
@@ -22358,7 +22592,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:18">
+    <row r="369" spans="1:18">
       <c r="A369" s="23"/>
       <c r="B369" s="11">
         <f t="shared" si="6"/>
@@ -22407,7 +22641,7 @@
         <v>45490</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:18">
+    <row r="370" spans="1:18">
       <c r="A370" s="23"/>
       <c r="B370" s="11">
         <f t="shared" si="6"/>
@@ -22460,7 +22694,7 @@
         <v>45495</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:18">
+    <row r="371" spans="1:18">
       <c r="A371" s="23"/>
       <c r="B371" s="11">
         <f t="shared" si="6"/>
@@ -22513,7 +22747,7 @@
         <v>45502</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:18">
+    <row r="372" spans="1:18">
       <c r="A372" s="23"/>
       <c r="B372" s="11">
         <f t="shared" si="6"/>
@@ -22562,7 +22796,7 @@
         <v>45504</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:18">
+    <row r="373" spans="1:18">
       <c r="A373" s="23"/>
       <c r="B373" s="11">
         <f t="shared" si="6"/>
@@ -22611,7 +22845,7 @@
         <v>45504</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:18">
+    <row r="374" spans="1:18">
       <c r="A374" s="23"/>
       <c r="B374" s="11">
         <f t="shared" si="6"/>
@@ -22664,7 +22898,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:18">
+    <row r="375" spans="1:18">
       <c r="A375" s="23"/>
       <c r="B375" s="11">
         <f t="shared" si="6"/>
@@ -22717,7 +22951,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:18">
+    <row r="376" spans="1:18">
       <c r="A376" s="23"/>
       <c r="B376" s="11">
         <f t="shared" si="6"/>
@@ -22766,7 +23000,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:18">
+    <row r="377" spans="1:18">
       <c r="A377" s="23"/>
       <c r="B377" s="11">
         <f t="shared" si="6"/>
@@ -22821,7 +23055,7 @@
         <v>45523</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:18">
+    <row r="378" spans="1:18">
       <c r="A378" s="23"/>
       <c r="B378" s="11">
         <f t="shared" si="6"/>
@@ -22868,7 +23102,7 @@
         <v>45525</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:18">
+    <row r="379" spans="1:18">
       <c r="A379" s="23"/>
       <c r="B379" s="11">
         <f t="shared" si="6"/>
@@ -22917,7 +23151,7 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:18">
+    <row r="380" spans="1:18">
       <c r="A380" s="23"/>
       <c r="B380" s="11">
         <f t="shared" si="6"/>
@@ -22966,7 +23200,7 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:18">
+    <row r="381" spans="1:18">
       <c r="A381" s="23"/>
       <c r="B381" s="11">
         <f t="shared" ref="B381:B444" si="7">ROW()-1</f>
@@ -23019,7 +23253,7 @@
         <v>45546</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:18">
+    <row r="382" spans="1:18">
       <c r="A382" s="23"/>
       <c r="B382" s="11">
         <f t="shared" si="7"/>
@@ -23068,7 +23302,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:18">
+    <row r="383" spans="1:18">
       <c r="A383" s="23"/>
       <c r="B383" s="11">
         <f t="shared" si="7"/>
@@ -23121,7 +23355,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:18">
+    <row r="384" spans="1:18">
       <c r="A384" s="23"/>
       <c r="B384" s="11">
         <f t="shared" si="7"/>
@@ -23170,7 +23404,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:18">
+    <row r="385" spans="1:18">
       <c r="A385" s="23"/>
       <c r="B385" s="11">
         <f t="shared" si="7"/>
@@ -23225,7 +23459,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:18">
+    <row r="386" spans="1:18">
       <c r="A386" s="23"/>
       <c r="B386" s="11">
         <f t="shared" si="7"/>
@@ -23280,7 +23514,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:18">
+    <row r="387" spans="1:18">
       <c r="A387" s="23"/>
       <c r="B387" s="11">
         <f t="shared" si="7"/>
@@ -23335,7 +23569,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:18">
+    <row r="388" spans="1:18">
       <c r="A388" s="23"/>
       <c r="B388" s="11">
         <f t="shared" si="7"/>
@@ -23390,7 +23624,7 @@
         <v>45581</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:18">
+    <row r="389" spans="1:18">
       <c r="A389" s="23"/>
       <c r="B389" s="11">
         <f t="shared" si="7"/>
@@ -23443,7 +23677,7 @@
         <v>45593</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:18">
+    <row r="390" spans="1:18">
       <c r="A390" s="23"/>
       <c r="B390" s="11">
         <f t="shared" si="7"/>
@@ -23490,7 +23724,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:18">
+    <row r="391" spans="1:18">
       <c r="A391" s="23"/>
       <c r="B391" s="11">
         <f t="shared" si="7"/>
@@ -23539,7 +23773,7 @@
         <v>45609</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:18">
+    <row r="392" spans="1:18">
       <c r="A392" s="23"/>
       <c r="B392" s="11">
         <f t="shared" si="7"/>
@@ -23588,7 +23822,7 @@
         <v>45621</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:18">
+    <row r="393" spans="1:18">
       <c r="A393" s="23"/>
       <c r="B393" s="11">
         <f t="shared" si="7"/>
@@ -23635,7 +23869,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:18">
+    <row r="394" spans="1:18">
       <c r="A394" s="23"/>
       <c r="B394" s="11">
         <f t="shared" si="7"/>
@@ -23682,7 +23916,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:18">
+    <row r="395" spans="1:18">
       <c r="A395" s="23"/>
       <c r="B395" s="11">
         <f t="shared" si="7"/>
@@ -23731,7 +23965,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:18">
+    <row r="396" spans="1:18">
       <c r="A396" s="23"/>
       <c r="B396" s="11">
         <f t="shared" si="7"/>
@@ -23780,7 +24014,7 @@
         <v>45630</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:18">
+    <row r="397" spans="1:18">
       <c r="A397" s="23"/>
       <c r="B397" s="11">
         <f t="shared" si="7"/>
@@ -23829,7 +24063,7 @@
         <v>45635</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:18">
+    <row r="398" spans="1:18">
       <c r="A398" s="23"/>
       <c r="B398" s="11">
         <f t="shared" si="7"/>
@@ -23882,7 +24116,7 @@
         <v>45635</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:18">
+    <row r="399" spans="1:18">
       <c r="A399" s="23"/>
       <c r="B399" s="11">
         <f t="shared" si="7"/>
@@ -23931,7 +24165,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:18">
+    <row r="400" spans="1:18">
       <c r="A400" s="23"/>
       <c r="B400" s="11">
         <f t="shared" si="7"/>
@@ -23978,7 +24212,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:18">
+    <row r="401" spans="1:18">
       <c r="A401" s="23"/>
       <c r="B401" s="11">
         <f t="shared" si="7"/>
@@ -24027,7 +24261,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:18">
+    <row r="402" spans="1:18">
       <c r="A402" s="23"/>
       <c r="B402" s="11">
         <f t="shared" si="7"/>
@@ -24076,7 +24310,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:18">
+    <row r="403" spans="1:18">
       <c r="A403" s="23"/>
       <c r="B403" s="11">
         <f t="shared" si="7"/>
@@ -24125,7 +24359,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:18">
+    <row r="404" spans="1:18">
       <c r="A404" s="23"/>
       <c r="B404" s="11">
         <f t="shared" si="7"/>
@@ -24174,7 +24408,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:18">
+    <row r="405" spans="1:18">
       <c r="A405" s="23"/>
       <c r="B405" s="11">
         <f t="shared" si="7"/>
@@ -24223,7 +24457,7 @@
         <v>45700</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:18">
+    <row r="406" spans="1:18">
       <c r="A406" s="23"/>
       <c r="B406" s="11">
         <f t="shared" si="7"/>
@@ -24272,7 +24506,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:18">
+    <row r="407" spans="1:18">
       <c r="A407" s="23"/>
       <c r="B407" s="11">
         <f t="shared" si="7"/>
@@ -24321,7 +24555,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:18">
+    <row r="408" spans="1:18">
       <c r="A408" s="23"/>
       <c r="B408" s="11">
         <f t="shared" si="7"/>
@@ -24374,7 +24608,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:18">
+    <row r="409" spans="1:18">
       <c r="A409" s="23"/>
       <c r="B409" s="11">
         <f t="shared" si="7"/>
@@ -24423,7 +24657,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:18">
+    <row r="410" spans="1:18">
       <c r="A410" s="23"/>
       <c r="B410" s="11">
         <f t="shared" si="7"/>
@@ -24476,7 +24710,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:18">
+    <row r="411" spans="1:18">
       <c r="A411" s="23"/>
       <c r="B411" s="11">
         <f t="shared" si="7"/>
@@ -24531,7 +24765,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:18">
+    <row r="412" spans="1:18">
       <c r="A412" s="23"/>
       <c r="B412" s="11">
         <f t="shared" si="7"/>
@@ -24586,7 +24820,7 @@
         <v>45742</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:18">
+    <row r="413" spans="1:18">
       <c r="A413" s="23"/>
       <c r="B413" s="11">
         <f t="shared" si="7"/>
@@ -24635,7 +24869,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:18">
+    <row r="414" spans="1:18">
       <c r="A414" s="23"/>
       <c r="B414" s="11">
         <f t="shared" si="7"/>
@@ -24684,7 +24918,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:18">
+    <row r="415" spans="1:18">
       <c r="A415" s="23"/>
       <c r="B415" s="11">
         <f t="shared" si="7"/>
@@ -24737,7 +24971,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:18">
+    <row r="416" spans="1:18">
       <c r="A416" s="23"/>
       <c r="B416" s="11">
         <f t="shared" si="7"/>
@@ -24792,7 +25026,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:18">
+    <row r="417" spans="1:18">
       <c r="A417" s="23"/>
       <c r="B417" s="11">
         <f t="shared" si="7"/>
@@ -24847,7 +25081,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:18">
+    <row r="418" spans="1:18">
       <c r="A418" s="23"/>
       <c r="B418" s="11">
         <f t="shared" si="7"/>
@@ -24894,7 +25128,7 @@
         <v>45763</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:18">
+    <row r="419" spans="1:18">
       <c r="A419" s="23"/>
       <c r="B419" s="11">
         <f t="shared" si="7"/>
@@ -24949,7 +25183,7 @@
         <v>45768</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:18">
+    <row r="420" spans="1:18">
       <c r="A420" s="23"/>
       <c r="B420" s="11">
         <f t="shared" si="7"/>
@@ -24996,7 +25230,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:18">
+    <row r="421" spans="1:18">
       <c r="A421" s="23"/>
       <c r="B421" s="11">
         <f t="shared" si="7"/>
@@ -25049,7 +25283,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:18">
+    <row r="422" spans="1:18">
       <c r="A422" s="23"/>
       <c r="B422" s="11">
         <f t="shared" si="7"/>
@@ -25098,7 +25332,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:18">
+    <row r="423" spans="1:18">
       <c r="A423" s="23"/>
       <c r="B423" s="11">
         <f t="shared" si="7"/>
@@ -25145,7 +25379,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:18">
+    <row r="424" spans="1:18">
       <c r="A424" s="23"/>
       <c r="B424" s="11">
         <f t="shared" si="7"/>
@@ -25198,7 +25432,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:18">
+    <row r="425" spans="1:18">
       <c r="A425" s="23"/>
       <c r="B425" s="11">
         <f t="shared" si="7"/>
@@ -25251,7 +25485,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:18">
+    <row r="426" spans="1:18">
       <c r="A426" s="23"/>
       <c r="B426" s="11">
         <f t="shared" si="7"/>
@@ -25298,7 +25532,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:18">
+    <row r="427" spans="1:18">
       <c r="A427" s="23"/>
       <c r="B427" s="11">
         <f t="shared" si="7"/>
@@ -25351,7 +25585,7 @@
         <v>45840</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:18">
+    <row r="428" spans="1:18">
       <c r="A428" s="23"/>
       <c r="B428" s="11">
         <f t="shared" si="7"/>
@@ -25406,7 +25640,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:18">
+    <row r="429" spans="1:18">
       <c r="A429" s="23"/>
       <c r="B429" s="11">
         <f t="shared" si="7"/>
@@ -25461,7 +25695,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:18">
+    <row r="430" spans="1:18">
       <c r="A430" s="23"/>
       <c r="B430" s="11">
         <f t="shared" si="7"/>
@@ -25514,7 +25748,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:18">
+    <row r="431" spans="1:18">
       <c r="A431" s="23"/>
       <c r="B431" s="11">
         <f t="shared" si="7"/>
@@ -25567,7 +25801,7 @@
         <v>45854</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:18">
+    <row r="432" spans="1:18">
       <c r="A432" s="23"/>
       <c r="B432" s="11">
         <f t="shared" si="7"/>
@@ -25618,7 +25852,7 @@
         <v>45859</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:18">
+    <row r="433" spans="1:18">
       <c r="A433" s="23"/>
       <c r="B433" s="11">
         <f t="shared" si="7"/>
@@ -25673,7 +25907,7 @@
         <v>45859</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:18">
+    <row r="434" spans="1:18">
       <c r="A434" s="23"/>
       <c r="B434" s="11">
         <f t="shared" si="7"/>
@@ -25726,7 +25960,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:18">
+    <row r="435" spans="1:18">
       <c r="A435" s="23"/>
       <c r="B435" s="11">
         <f t="shared" si="7"/>
@@ -25779,7 +26013,7 @@
         <v>45875</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:18">
+    <row r="436" spans="1:18">
       <c r="A436" s="20"/>
       <c r="B436" s="11">
         <f t="shared" si="7"/>
@@ -25834,7 +26068,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:18">
+    <row r="437" spans="1:18">
       <c r="A437" s="20"/>
       <c r="B437" s="11">
         <f t="shared" si="7"/>
@@ -25889,7 +26123,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:18">
+    <row r="438" spans="1:18">
       <c r="A438" s="20"/>
       <c r="B438" s="11">
         <f t="shared" si="7"/>
@@ -25942,7 +26176,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:18">
+    <row r="439" spans="1:18">
       <c r="A439" s="20"/>
       <c r="B439" s="11">
         <f t="shared" si="7"/>
@@ -25995,7 +26229,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:18">
+    <row r="440" spans="1:18">
       <c r="A440" s="20"/>
       <c r="B440" s="11">
         <f t="shared" si="7"/>
@@ -26048,7 +26282,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:18">
+    <row r="441" spans="1:18">
       <c r="A441" s="20"/>
       <c r="B441" s="11">
         <f t="shared" si="7"/>
@@ -26097,7 +26331,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:18">
+    <row r="442" spans="1:18">
       <c r="A442" s="20"/>
       <c r="B442" s="11">
         <f t="shared" si="7"/>
@@ -26146,7 +26380,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="443" hidden="1" spans="1:18">
+    <row r="443" spans="1:18">
       <c r="A443" s="20"/>
       <c r="B443" s="11">
         <f t="shared" si="7"/>
@@ -26250,7 +26484,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:18">
+    <row r="445" spans="1:18">
       <c r="A445" s="20"/>
       <c r="B445" s="11">
         <f t="shared" ref="B445:B505" si="8">ROW()-1</f>
@@ -26299,7 +26533,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:18">
+    <row r="446" spans="1:18">
       <c r="A446" s="20"/>
       <c r="B446" s="11">
         <f t="shared" si="8"/>
@@ -26352,7 +26586,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:18">
+    <row r="447" spans="1:18">
       <c r="A447" s="20"/>
       <c r="B447" s="11">
         <f t="shared" si="8"/>
@@ -26403,7 +26637,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:18">
+    <row r="448" spans="1:18">
       <c r="A448" s="20"/>
       <c r="B448" s="11">
         <f t="shared" si="8"/>
@@ -26503,7 +26737,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:18">
+    <row r="450" spans="1:18">
       <c r="A450" s="20" t="s">
         <v>729</v>
       </c>
@@ -26554,7 +26788,7 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:18">
+    <row r="451" spans="1:18">
       <c r="A451" s="20"/>
       <c r="B451" s="11">
         <f t="shared" si="8"/>
@@ -26601,7 +26835,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="452" hidden="1" spans="1:18">
+    <row r="452" spans="1:18">
       <c r="A452" s="20"/>
       <c r="B452" s="11">
         <f t="shared" si="8"/>
@@ -26654,7 +26888,7 @@
         <v>46020</v>
       </c>
     </row>
-    <row r="453" hidden="1" spans="1:18">
+    <row r="453" spans="1:18">
       <c r="A453" s="20"/>
       <c r="B453" s="11">
         <f t="shared" si="8"/>
@@ -26707,7 +26941,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="454" hidden="1" spans="1:18">
+    <row r="454" spans="1:18">
       <c r="A454" s="20"/>
       <c r="B454" s="11">
         <f t="shared" si="8"/>
@@ -26758,7 +26992,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="455" hidden="1" spans="1:18">
+    <row r="455" spans="1:18">
       <c r="A455" s="20"/>
       <c r="B455" s="11">
         <f t="shared" si="8"/>
@@ -26811,7 +27045,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="456" hidden="1" spans="1:18">
+    <row r="456" spans="1:18">
       <c r="A456" s="23" t="s">
         <v>738</v>
       </c>
@@ -26862,7 +27096,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:18">
+    <row r="457" spans="1:18">
       <c r="A457" s="23"/>
       <c r="B457" s="11">
         <f t="shared" si="8"/>
@@ -26917,7 +27151,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="458" hidden="1" spans="1:18">
+    <row r="458" spans="1:18">
       <c r="A458" s="23"/>
       <c r="B458" s="11">
         <f t="shared" si="8"/>
@@ -26964,7 +27198,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="459" hidden="1" spans="1:18">
+    <row r="459" spans="1:18">
       <c r="A459" s="23"/>
       <c r="B459" s="11">
         <f t="shared" si="8"/>
@@ -27013,7 +27247,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:18">
+    <row r="460" spans="1:18">
       <c r="A460" s="23"/>
       <c r="B460" s="11">
         <f t="shared" si="8"/>
@@ -27066,7 +27300,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="461" hidden="1" spans="1:18">
+    <row r="461" spans="1:18">
       <c r="A461" s="23"/>
       <c r="B461" s="11">
         <f t="shared" si="8"/>
@@ -27115,7 +27349,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="462" hidden="1" spans="1:18">
+    <row r="462" spans="1:18">
       <c r="A462" s="23"/>
       <c r="B462" s="11">
         <f t="shared" si="8"/>
@@ -27164,7 +27398,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="463" hidden="1" spans="1:18">
+    <row r="463" spans="1:18">
       <c r="A463" s="23"/>
       <c r="B463" s="11">
         <f t="shared" si="8"/>
@@ -27258,7 +27492,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:18">
+    <row r="465" spans="1:18">
       <c r="A465" s="23"/>
       <c r="B465" s="11">
         <f t="shared" si="8"/>
@@ -27313,7 +27547,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:18">
+    <row r="466" spans="1:18">
       <c r="A466" s="23"/>
       <c r="B466" s="11">
         <f t="shared" si="8"/>
@@ -27362,7 +27596,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="467" hidden="1" spans="1:18">
+    <row r="467" spans="1:18">
       <c r="A467" s="23"/>
       <c r="B467" s="11">
         <f t="shared" si="8"/>
@@ -27409,7 +27643,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="468" hidden="1" spans="1:18">
+    <row r="468" spans="1:18">
       <c r="A468" s="23"/>
       <c r="B468" s="11">
         <f t="shared" si="8"/>
@@ -27462,7 +27696,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="469" hidden="1" spans="1:18">
+    <row r="469" spans="1:18">
       <c r="A469" s="23"/>
       <c r="B469" s="11">
         <f t="shared" si="8"/>
@@ -27511,7 +27745,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="470" hidden="1" spans="1:18">
+    <row r="470" spans="1:18">
       <c r="A470" s="23"/>
       <c r="B470" s="11">
         <f t="shared" si="8"/>
@@ -27564,7 +27798,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="471" hidden="1" spans="1:18">
+    <row r="471" spans="1:18">
       <c r="A471" s="23"/>
       <c r="B471" s="11">
         <f t="shared" si="8"/>
@@ -27617,7 +27851,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="472" hidden="1" spans="1:18">
+    <row r="472" spans="1:18">
       <c r="A472" s="23"/>
       <c r="B472" s="11">
         <f t="shared" si="8"/>
@@ -27721,7 +27955,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="474" hidden="1" spans="1:18">
+    <row r="474" spans="1:18">
       <c r="A474" s="23"/>
       <c r="B474" s="11">
         <f t="shared" si="8"/>
@@ -27776,7 +28010,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="475" hidden="1" spans="1:18">
+    <row r="475" spans="1:18">
       <c r="A475" s="23"/>
       <c r="B475" s="11">
         <f t="shared" si="8"/>
@@ -27829,7 +28063,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="476" hidden="1" spans="1:18">
+    <row r="476" spans="1:18">
       <c r="A476" s="23"/>
       <c r="B476" s="11">
         <f t="shared" si="8"/>
@@ -27882,7 +28116,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="477" hidden="1" spans="1:18">
+    <row r="477" spans="1:18">
       <c r="A477" s="23"/>
       <c r="B477" s="11">
         <f t="shared" si="8"/>
@@ -27931,7 +28165,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="478" hidden="1" spans="1:18">
+    <row r="478" spans="1:18">
       <c r="A478" s="23"/>
       <c r="B478" s="11">
         <f t="shared" si="8"/>
@@ -27984,7 +28218,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="479" hidden="1" spans="1:18">
+    <row r="479" spans="1:18">
       <c r="A479" s="23"/>
       <c r="B479" s="11">
         <f t="shared" si="8"/>
@@ -28037,7 +28271,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="480" hidden="1" spans="1:18">
+    <row r="480" spans="1:18">
       <c r="A480" s="23"/>
       <c r="B480" s="11">
         <f t="shared" si="8"/>
@@ -28090,7 +28324,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="481" hidden="1" spans="1:18">
+    <row r="481" spans="1:18">
       <c r="A481" s="23"/>
       <c r="B481" s="11">
         <f t="shared" si="8"/>
@@ -28143,7 +28377,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="482" hidden="1" spans="1:18">
+    <row r="482" spans="1:18">
       <c r="A482" s="23"/>
       <c r="B482" s="11">
         <f t="shared" si="8"/>
@@ -28190,7 +28424,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="483" hidden="1" spans="1:18">
+    <row r="483" spans="1:18">
       <c r="A483" s="23"/>
       <c r="B483" s="11">
         <f t="shared" si="8"/>
@@ -28245,7 +28479,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="484" hidden="1" spans="1:18">
+    <row r="484" spans="1:18">
       <c r="A484" s="23"/>
       <c r="B484" s="11">
         <f t="shared" si="8"/>
@@ -28296,7 +28530,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="485" hidden="1" spans="1:18">
+    <row r="485" spans="1:18">
       <c r="A485" s="23"/>
       <c r="B485" s="11">
         <f t="shared" si="8"/>
@@ -28347,7 +28581,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="486" hidden="1" spans="1:18">
+    <row r="486" spans="1:18">
       <c r="A486" s="23"/>
       <c r="B486" s="11">
         <f t="shared" si="8"/>
@@ -28402,7 +28636,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="487" hidden="1" spans="1:18">
+    <row r="487" spans="1:18">
       <c r="A487" s="23"/>
       <c r="B487" s="11">
         <f t="shared" si="8"/>
@@ -28455,7 +28689,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="488" hidden="1" spans="1:18">
+    <row r="488" spans="1:18">
       <c r="A488" s="23"/>
       <c r="B488" s="11">
         <f t="shared" si="8"/>
@@ -28510,7 +28744,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="489" hidden="1" spans="1:18">
+    <row r="489" spans="1:18">
       <c r="A489" s="23"/>
       <c r="B489" s="11">
         <f t="shared" si="8"/>
@@ -28563,7 +28797,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="490" hidden="1" spans="1:18">
+    <row r="490" spans="1:18">
       <c r="A490" s="23"/>
       <c r="B490" s="11">
         <f t="shared" si="8"/>
@@ -28612,7 +28846,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="491" hidden="1" spans="1:18">
+    <row r="491" spans="1:18">
       <c r="A491" s="23"/>
       <c r="B491" s="11">
         <f t="shared" si="8"/>
@@ -28665,7 +28899,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="492" hidden="1" spans="1:18">
+    <row r="492" spans="1:18">
       <c r="A492" s="23"/>
       <c r="B492" s="11">
         <f t="shared" si="8"/>
@@ -28714,7 +28948,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="493" hidden="1" spans="1:18">
+    <row r="493" spans="1:18">
       <c r="A493" s="23"/>
       <c r="B493" s="11">
         <f t="shared" si="8"/>
@@ -28759,7 +28993,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="494" hidden="1" spans="1:18">
+    <row r="494" spans="1:18">
       <c r="A494" s="23"/>
       <c r="B494" s="11">
         <f t="shared" si="8"/>
@@ -28812,7 +29046,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="495" hidden="1" spans="1:18">
+    <row r="495" spans="1:18">
       <c r="A495" s="23"/>
       <c r="B495" s="11">
         <f t="shared" si="8"/>
@@ -28865,7 +29099,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="496" hidden="1" spans="1:18">
+    <row r="496" spans="1:18">
       <c r="A496" s="23"/>
       <c r="B496" s="11">
         <f t="shared" si="8"/>
@@ -28918,7 +29152,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="497" hidden="1" spans="1:18">
+    <row r="497" spans="1:18">
       <c r="A497" s="23"/>
       <c r="B497" s="11">
         <f t="shared" si="8"/>
@@ -28971,7 +29205,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="498" hidden="1" spans="1:18">
+    <row r="498" spans="1:18">
       <c r="A498" s="23"/>
       <c r="B498" s="11">
         <f t="shared" si="8"/>
@@ -29024,7 +29258,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="499" hidden="1" spans="1:18">
+    <row r="499" spans="1:18">
       <c r="A499" s="23"/>
       <c r="B499" s="11">
         <f t="shared" si="8"/>
@@ -29077,7 +29311,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="500" hidden="1" spans="1:18">
+    <row r="500" spans="1:18">
       <c r="A500" s="23"/>
       <c r="B500" s="11">
         <f t="shared" si="8"/>
@@ -29130,7 +29364,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="501" hidden="1" spans="1:18">
+    <row r="501" spans="1:18">
       <c r="A501" s="23"/>
       <c r="B501" s="11">
         <f t="shared" si="8"/>
@@ -29383,298 +29617,1861 @@
         <v>46204</v>
       </c>
     </row>
+    <row r="506" spans="1:18">
+      <c r="A506" s="47"/>
+      <c r="B506" s="11">
+        <f t="shared" ref="B506:B515" si="9">ROW()-1</f>
+        <v>505</v>
+      </c>
+      <c r="C506" s="48" t="s">
+        <v>797</v>
+      </c>
+      <c r="D506" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E506" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F506" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G506" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H506" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="I506" s="48"/>
+      <c r="J506" s="48"/>
+      <c r="K506" s="48"/>
+      <c r="L506" s="48"/>
+      <c r="M506" s="49" t="s">
+        <v>799</v>
+      </c>
+      <c r="N506" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O506" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P506" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q506" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R506" s="50">
+        <v>44440</v>
+      </c>
+    </row>
+    <row r="507" spans="1:18">
+      <c r="A507" s="47"/>
+      <c r="B507" s="11">
+        <f t="shared" si="9"/>
+        <v>506</v>
+      </c>
+      <c r="C507" s="48" t="s">
+        <v>800</v>
+      </c>
+      <c r="D507" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E507" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F507" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G507" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H507" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I507" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J507" s="48" t="s">
+        <v>803</v>
+      </c>
+      <c r="K507" s="48"/>
+      <c r="L507" s="48"/>
+      <c r="M507" s="48" t="s">
+        <v>804</v>
+      </c>
+      <c r="N507" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O507" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P507" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q507" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R507" s="51">
+        <v>44623</v>
+      </c>
+    </row>
+    <row r="508" spans="1:18">
+      <c r="A508" s="47"/>
+      <c r="B508" s="11">
+        <f t="shared" si="9"/>
+        <v>507</v>
+      </c>
+      <c r="C508" s="48" t="s">
+        <v>805</v>
+      </c>
+      <c r="D508" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E508" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F508" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G508" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H508" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I508" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="J508" s="48"/>
+      <c r="K508" s="48"/>
+      <c r="L508" s="48"/>
+      <c r="M508" s="49" t="s">
+        <v>808</v>
+      </c>
+      <c r="N508" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O508" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P508" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q508" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R508" s="51">
+        <v>44634</v>
+      </c>
+    </row>
+    <row r="509" spans="1:18">
+      <c r="A509" s="47"/>
+      <c r="B509" s="11">
+        <f t="shared" si="9"/>
+        <v>508</v>
+      </c>
+      <c r="C509" s="48" t="s">
+        <v>809</v>
+      </c>
+      <c r="D509" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E509" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F509" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G509" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H509" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I509" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J509" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K509" s="48"/>
+      <c r="L509" s="48"/>
+      <c r="M509" s="48" t="s">
+        <v>804</v>
+      </c>
+      <c r="N509" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O509" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P509" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q509" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R509" s="51">
+        <v>44670</v>
+      </c>
+    </row>
+    <row r="510" spans="1:18">
+      <c r="A510" s="47"/>
+      <c r="B510" s="11">
+        <f t="shared" si="9"/>
+        <v>509</v>
+      </c>
+      <c r="C510" s="48" t="s">
+        <v>811</v>
+      </c>
+      <c r="D510" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E510" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F510" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G510" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H510" s="48" t="s">
+        <v>812</v>
+      </c>
+      <c r="I510" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J510" s="48"/>
+      <c r="K510" s="48"/>
+      <c r="L510" s="48"/>
+      <c r="M510" s="48" t="s">
+        <v>339</v>
+      </c>
+      <c r="N510" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="O510" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="P510" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q510" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R510" s="51">
+        <v>44673</v>
+      </c>
+    </row>
+    <row r="511" spans="1:18">
+      <c r="A511" s="47"/>
+      <c r="B511" s="11">
+        <f t="shared" si="9"/>
+        <v>510</v>
+      </c>
+      <c r="C511" s="48" t="s">
+        <v>814</v>
+      </c>
+      <c r="D511" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E511" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F511" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G511" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H511" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I511" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J511" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K511" s="48"/>
+      <c r="L511" s="48"/>
+      <c r="M511" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N511" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O511" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P511" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q511" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R511" s="51">
+        <v>44954</v>
+      </c>
+    </row>
+    <row r="512" spans="1:18">
+      <c r="A512" s="47"/>
+      <c r="B512" s="11">
+        <f t="shared" si="9"/>
+        <v>511</v>
+      </c>
+      <c r="C512" s="48" t="s">
+        <v>816</v>
+      </c>
+      <c r="D512" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E512" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F512" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G512" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H512" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I512" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J512" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K512" s="48"/>
+      <c r="L512" s="48"/>
+      <c r="M512" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N512" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O512" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P512" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q512" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R512" s="51">
+        <v>44966</v>
+      </c>
+    </row>
+    <row r="513" spans="1:18">
+      <c r="A513" s="47"/>
+      <c r="B513" s="11">
+        <f t="shared" si="9"/>
+        <v>512</v>
+      </c>
+      <c r="C513" s="48" t="s">
+        <v>817</v>
+      </c>
+      <c r="D513" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E513" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F513" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G513" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H513" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I513" s="48" t="s">
+        <v>818</v>
+      </c>
+      <c r="J513" s="48"/>
+      <c r="K513" s="48"/>
+      <c r="L513" s="48"/>
+      <c r="M513" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N513" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O513" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P513" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q513" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R513" s="51">
+        <v>44965</v>
+      </c>
+    </row>
+    <row r="514" spans="1:18">
+      <c r="A514" s="47"/>
+      <c r="B514" s="11">
+        <f t="shared" si="9"/>
+        <v>513</v>
+      </c>
+      <c r="C514" s="48" t="s">
+        <v>819</v>
+      </c>
+      <c r="D514" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E514" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F514" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G514" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H514" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I514" s="48" t="s">
+        <v>818</v>
+      </c>
+      <c r="J514" s="48"/>
+      <c r="K514" s="48"/>
+      <c r="L514" s="48"/>
+      <c r="M514" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N514" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O514" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P514" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q514" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R514" s="51">
+        <v>44971</v>
+      </c>
+    </row>
+    <row r="515" spans="1:18">
+      <c r="A515" s="47"/>
+      <c r="B515" s="11">
+        <f t="shared" si="9"/>
+        <v>514</v>
+      </c>
+      <c r="C515" s="48" t="s">
+        <v>820</v>
+      </c>
+      <c r="D515" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E515" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F515" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G515" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H515" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I515" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J515" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K515" s="48"/>
+      <c r="L515" s="48"/>
+      <c r="M515" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N515" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O515" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P515" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q515" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R515" s="51">
+        <v>44973</v>
+      </c>
+    </row>
+    <row r="516" spans="1:18">
+      <c r="A516" s="47"/>
+      <c r="B516" s="11">
+        <f t="shared" ref="B516:B525" si="10">ROW()-1</f>
+        <v>515</v>
+      </c>
+      <c r="C516" s="48" t="s">
+        <v>821</v>
+      </c>
+      <c r="D516" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E516" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F516" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G516" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H516" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I516" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J516" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K516" s="48"/>
+      <c r="L516" s="48"/>
+      <c r="M516" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N516" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O516" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P516" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q516" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R516" s="51">
+        <v>44984</v>
+      </c>
+    </row>
+    <row r="517" spans="1:18">
+      <c r="A517" s="52"/>
+      <c r="B517" s="11">
+        <f t="shared" si="10"/>
+        <v>516</v>
+      </c>
+      <c r="C517" s="48" t="s">
+        <v>822</v>
+      </c>
+      <c r="D517" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E517" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F517" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G517" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H517" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I517" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J517" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K517" s="48"/>
+      <c r="L517" s="48"/>
+      <c r="M517" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N517" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O517" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P517" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q517" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R517" s="51">
+        <v>44991</v>
+      </c>
+    </row>
+    <row r="518" spans="1:18">
+      <c r="A518" s="52"/>
+      <c r="B518" s="11">
+        <f t="shared" si="10"/>
+        <v>517</v>
+      </c>
+      <c r="C518" s="48" t="s">
+        <v>823</v>
+      </c>
+      <c r="D518" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E518" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F518" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G518" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H518" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I518" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="J518" s="48"/>
+      <c r="K518" s="48"/>
+      <c r="L518" s="48"/>
+      <c r="M518" s="48" t="s">
+        <v>824</v>
+      </c>
+      <c r="N518" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O518" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P518" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q518" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R518" s="51">
+        <v>44993</v>
+      </c>
+    </row>
+    <row r="519" spans="1:18">
+      <c r="A519" s="52"/>
+      <c r="B519" s="11">
+        <f t="shared" si="10"/>
+        <v>518</v>
+      </c>
+      <c r="C519" s="48" t="s">
+        <v>825</v>
+      </c>
+      <c r="D519" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E519" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F519" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G519" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H519" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I519" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="J519" s="48"/>
+      <c r="K519" s="48"/>
+      <c r="L519" s="48"/>
+      <c r="M519" s="48" t="s">
+        <v>824</v>
+      </c>
+      <c r="N519" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O519" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P519" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q519" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R519" s="51">
+        <v>45015</v>
+      </c>
+    </row>
+    <row r="520" spans="1:18">
+      <c r="A520" s="52"/>
+      <c r="B520" s="11">
+        <f t="shared" si="10"/>
+        <v>519</v>
+      </c>
+      <c r="C520" s="48" t="s">
+        <v>826</v>
+      </c>
+      <c r="D520" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E520" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F520" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G520" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H520" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I520" s="48" t="s">
+        <v>827</v>
+      </c>
+      <c r="J520" s="48"/>
+      <c r="K520" s="48"/>
+      <c r="L520" s="48"/>
+      <c r="M520" s="48" t="s">
+        <v>828</v>
+      </c>
+      <c r="N520" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O520" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P520" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q520" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R520" s="51">
+        <v>45028</v>
+      </c>
+    </row>
+    <row r="521" spans="1:18">
+      <c r="A521" s="47"/>
+      <c r="B521" s="11">
+        <f t="shared" si="10"/>
+        <v>520</v>
+      </c>
+      <c r="C521" s="48" t="s">
+        <v>829</v>
+      </c>
+      <c r="D521" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E521" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F521" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G521" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H521" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I521" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J521" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K521" s="48"/>
+      <c r="L521" s="48"/>
+      <c r="M521" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N521" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O521" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P521" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q521" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R521" s="51">
+        <v>45029</v>
+      </c>
+    </row>
+    <row r="522" spans="1:18">
+      <c r="A522" s="47"/>
+      <c r="B522" s="11">
+        <f t="shared" si="10"/>
+        <v>521</v>
+      </c>
+      <c r="C522" s="48" t="s">
+        <v>830</v>
+      </c>
+      <c r="D522" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E522" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F522" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G522" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H522" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I522" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J522" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K522" s="48"/>
+      <c r="L522" s="48"/>
+      <c r="M522" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N522" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O522" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P522" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q522" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R522" s="51">
+        <v>45040</v>
+      </c>
+    </row>
+    <row r="523" spans="1:18">
+      <c r="A523" s="52"/>
+      <c r="B523" s="11">
+        <f t="shared" si="10"/>
+        <v>522</v>
+      </c>
+      <c r="C523" s="48" t="s">
+        <v>831</v>
+      </c>
+      <c r="D523" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E523" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F523" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G523" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H523" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I523" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J523" s="48" t="s">
+        <v>810</v>
+      </c>
+      <c r="K523" s="48"/>
+      <c r="L523" s="48"/>
+      <c r="M523" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N523" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O523" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P523" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q523" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R523" s="51">
+        <v>45062</v>
+      </c>
+    </row>
+    <row r="524" spans="1:18">
+      <c r="A524" s="47"/>
+      <c r="B524" s="11">
+        <f t="shared" si="10"/>
+        <v>523</v>
+      </c>
+      <c r="C524" s="48" t="s">
+        <v>832</v>
+      </c>
+      <c r="D524" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E524" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F524" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G524" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H524" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I524" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J524" s="48"/>
+      <c r="K524" s="48"/>
+      <c r="L524" s="48"/>
+      <c r="M524" s="48" t="s">
+        <v>834</v>
+      </c>
+      <c r="N524" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O524" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P524" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q524" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R524" s="51">
+        <v>45077</v>
+      </c>
+    </row>
+    <row r="525" spans="1:18">
+      <c r="A525" s="47"/>
+      <c r="B525" s="11">
+        <f t="shared" si="10"/>
+        <v>524</v>
+      </c>
+      <c r="C525" s="48" t="s">
+        <v>835</v>
+      </c>
+      <c r="D525" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E525" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F525" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G525" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H525" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I525" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J525" s="48"/>
+      <c r="K525" s="48"/>
+      <c r="L525" s="48"/>
+      <c r="M525" s="48" t="s">
+        <v>834</v>
+      </c>
+      <c r="N525" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O525" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P525" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q525" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R525" s="51">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="526" spans="1:18">
+      <c r="A526" s="47"/>
+      <c r="B526" s="11">
+        <f t="shared" ref="B526:B536" si="11">ROW()-1</f>
+        <v>525</v>
+      </c>
+      <c r="C526" s="48" t="s">
+        <v>836</v>
+      </c>
+      <c r="D526" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E526" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F526" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G526" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H526" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I526" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="J526" s="48"/>
+      <c r="K526" s="48"/>
+      <c r="L526" s="48"/>
+      <c r="M526" s="48" t="s">
+        <v>824</v>
+      </c>
+      <c r="N526" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O526" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P526" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q526" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R526" s="51">
+        <v>45370</v>
+      </c>
+    </row>
+    <row r="527" spans="1:18">
+      <c r="A527" s="47"/>
+      <c r="B527" s="11">
+        <f t="shared" si="11"/>
+        <v>526</v>
+      </c>
+      <c r="C527" s="48" t="s">
+        <v>837</v>
+      </c>
+      <c r="D527" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E527" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F527" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G527" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H527" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I527" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J527" s="48"/>
+      <c r="K527" s="48"/>
+      <c r="L527" s="48"/>
+      <c r="M527" s="48" t="s">
+        <v>834</v>
+      </c>
+      <c r="N527" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O527" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P527" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q527" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R527" s="51">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="528" spans="1:18">
+      <c r="A528" s="47"/>
+      <c r="B528" s="11">
+        <f t="shared" si="11"/>
+        <v>527</v>
+      </c>
+      <c r="C528" s="48" t="s">
+        <v>838</v>
+      </c>
+      <c r="D528" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E528" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F528" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G528" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H528" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I528" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J528" s="48"/>
+      <c r="K528" s="48"/>
+      <c r="L528" s="48"/>
+      <c r="M528" s="48" t="s">
+        <v>839</v>
+      </c>
+      <c r="N528" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O528" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P528" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q528" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R528" s="51">
+        <v>45470</v>
+      </c>
+    </row>
+    <row r="529" spans="1:18">
+      <c r="A529" s="47"/>
+      <c r="B529" s="11">
+        <f t="shared" si="11"/>
+        <v>528</v>
+      </c>
+      <c r="C529" s="48" t="s">
+        <v>840</v>
+      </c>
+      <c r="D529" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E529" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F529" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G529" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H529" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I529" s="48" t="s">
+        <v>827</v>
+      </c>
+      <c r="J529" s="48"/>
+      <c r="K529" s="48"/>
+      <c r="L529" s="48"/>
+      <c r="M529" s="48" t="s">
+        <v>841</v>
+      </c>
+      <c r="N529" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O529" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P529" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q529" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R529" s="51">
+        <v>45538</v>
+      </c>
+    </row>
+    <row r="530" spans="1:18">
+      <c r="A530" s="47"/>
+      <c r="B530" s="11">
+        <f t="shared" si="11"/>
+        <v>529</v>
+      </c>
+      <c r="C530" s="48" t="s">
+        <v>842</v>
+      </c>
+      <c r="D530" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E530" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F530" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G530" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H530" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I530" s="48" t="s">
+        <v>843</v>
+      </c>
+      <c r="J530" s="48"/>
+      <c r="K530" s="48"/>
+      <c r="L530" s="48"/>
+      <c r="M530" s="48" t="s">
+        <v>844</v>
+      </c>
+      <c r="N530" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O530" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="P530" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q530" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R530" s="51">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="531" spans="1:18">
+      <c r="A531" s="47"/>
+      <c r="B531" s="11">
+        <f t="shared" si="11"/>
+        <v>530</v>
+      </c>
+      <c r="C531" s="48" t="s">
+        <v>845</v>
+      </c>
+      <c r="D531" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E531" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F531" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G531" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H531" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I531" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="J531" s="48"/>
+      <c r="K531" s="48"/>
+      <c r="L531" s="48"/>
+      <c r="M531" s="48" t="s">
+        <v>846</v>
+      </c>
+      <c r="N531" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O531" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P531" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q531" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R531" s="51">
+        <v>45854</v>
+      </c>
+    </row>
+    <row r="532" spans="1:18">
+      <c r="A532" s="47"/>
+      <c r="B532" s="11">
+        <f t="shared" si="11"/>
+        <v>531</v>
+      </c>
+      <c r="C532" s="48" t="s">
+        <v>847</v>
+      </c>
+      <c r="D532" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E532" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F532" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G532" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H532" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I532" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J532" s="48"/>
+      <c r="K532" s="48"/>
+      <c r="L532" s="48"/>
+      <c r="M532" s="48" t="s">
+        <v>848</v>
+      </c>
+      <c r="N532" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O532" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P532" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q532" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R532" s="51">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="533" spans="1:18">
+      <c r="A533" s="47"/>
+      <c r="B533" s="11">
+        <f t="shared" si="11"/>
+        <v>532</v>
+      </c>
+      <c r="C533" s="48" t="s">
+        <v>849</v>
+      </c>
+      <c r="D533" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E533" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F533" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G533" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H533" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I533" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J533" s="48"/>
+      <c r="K533" s="48"/>
+      <c r="L533" s="48"/>
+      <c r="M533" s="48" t="s">
+        <v>834</v>
+      </c>
+      <c r="N533" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O533" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="P533" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q533" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R533" s="51">
+        <v>45882</v>
+      </c>
+    </row>
+    <row r="534" spans="1:18">
+      <c r="A534" s="47"/>
+      <c r="B534" s="11">
+        <f t="shared" si="11"/>
+        <v>533</v>
+      </c>
+      <c r="C534" s="53" t="s">
+        <v>850</v>
+      </c>
+      <c r="D534" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E534" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F534" s="53" t="s">
+        <v>798</v>
+      </c>
+      <c r="G534" s="53" t="s">
+        <v>798</v>
+      </c>
+      <c r="H534" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I534" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="J534" s="53"/>
+      <c r="K534" s="53"/>
+      <c r="L534" s="53"/>
+      <c r="M534" s="53" t="s">
+        <v>834</v>
+      </c>
+      <c r="N534" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="O534" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="P534" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q534" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="R534" s="55">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="535" spans="1:18">
+      <c r="A535" s="47"/>
+      <c r="B535" s="11">
+        <f t="shared" si="11"/>
+        <v>534</v>
+      </c>
+      <c r="C535" s="53" t="s">
+        <v>851</v>
+      </c>
+      <c r="D535" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E535" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F535" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G535" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H535" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I535" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J535" s="48" t="s">
+        <v>803</v>
+      </c>
+      <c r="K535" s="48"/>
+      <c r="L535" s="48"/>
+      <c r="M535" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N535" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O535" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P535" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q535" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R535" s="51">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="536" spans="1:18">
+      <c r="A536" s="47"/>
+      <c r="B536" s="11">
+        <f t="shared" si="11"/>
+        <v>535</v>
+      </c>
+      <c r="C536" s="53" t="s">
+        <v>852</v>
+      </c>
+      <c r="D536" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E536" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F536" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="G536" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="H536" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="I536" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="J536" s="48" t="s">
+        <v>803</v>
+      </c>
+      <c r="K536" s="48"/>
+      <c r="L536" s="48"/>
+      <c r="M536" s="48" t="s">
+        <v>815</v>
+      </c>
+      <c r="N536" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="O536" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P536" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q536" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="R536" s="51">
+        <v>46195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R505" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" dxfId="0" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="0" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="0" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C94">
-    <cfRule type="duplicateValues" dxfId="0" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C146">
-    <cfRule type="duplicateValues" dxfId="0" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="0" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C210">
-    <cfRule type="duplicateValues" dxfId="0" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C211">
-    <cfRule type="duplicateValues" dxfId="0" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C214">
-    <cfRule type="duplicateValues" dxfId="0" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="duplicateValues" dxfId="0" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218">
-    <cfRule type="duplicateValues" dxfId="0" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C221">
-    <cfRule type="duplicateValues" dxfId="0" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C222">
-    <cfRule type="duplicateValues" dxfId="0" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C223">
-    <cfRule type="duplicateValues" dxfId="0" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C224">
-    <cfRule type="duplicateValues" dxfId="0" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C225">
-    <cfRule type="duplicateValues" dxfId="0" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I280">
-    <cfRule type="duplicateValues" dxfId="1" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I345">
-    <cfRule type="duplicateValues" dxfId="1" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I396">
-    <cfRule type="duplicateValues" dxfId="1" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C449">
-    <cfRule type="duplicateValues" dxfId="2" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C450">
+    <cfRule type="duplicateValues" dxfId="2" priority="184"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C451">
+    <cfRule type="duplicateValues" dxfId="2" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C452">
+    <cfRule type="duplicateValues" dxfId="2" priority="179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C453">
+    <cfRule type="duplicateValues" dxfId="2" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C454">
+    <cfRule type="duplicateValues" dxfId="2" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C455">
+    <cfRule type="duplicateValues" dxfId="2" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C456">
+    <cfRule type="duplicateValues" dxfId="2" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C457">
+    <cfRule type="duplicateValues" dxfId="2" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C458">
+    <cfRule type="duplicateValues" dxfId="2" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C459">
     <cfRule type="duplicateValues" dxfId="2" priority="155"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C451">
-    <cfRule type="duplicateValues" dxfId="2" priority="152"/>
+  <conditionalFormatting sqref="C460">
+    <cfRule type="duplicateValues" dxfId="2" priority="154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C452">
+  <conditionalFormatting sqref="C461">
     <cfRule type="duplicateValues" dxfId="2" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C453">
+  <conditionalFormatting sqref="C462">
+    <cfRule type="duplicateValues" dxfId="2" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C463">
     <cfRule type="duplicateValues" dxfId="2" priority="147"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C454">
+  <conditionalFormatting sqref="C464">
     <cfRule type="duplicateValues" dxfId="2" priority="145"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C455">
+  <conditionalFormatting sqref="C465">
     <cfRule type="duplicateValues" dxfId="2" priority="143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C456">
-    <cfRule type="duplicateValues" dxfId="2" priority="137"/>
+  <conditionalFormatting sqref="C466">
+    <cfRule type="duplicateValues" dxfId="2" priority="140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C457">
-    <cfRule type="duplicateValues" dxfId="2" priority="134"/>
+  <conditionalFormatting sqref="C467">
+    <cfRule type="duplicateValues" dxfId="2" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C458">
+  <conditionalFormatting sqref="C468">
+    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C469">
+    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C470">
     <cfRule type="duplicateValues" dxfId="2" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C459">
+  <conditionalFormatting sqref="C471">
     <cfRule type="duplicateValues" dxfId="2" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C460">
+  <conditionalFormatting sqref="C472">
     <cfRule type="duplicateValues" dxfId="2" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C461">
-    <cfRule type="duplicateValues" dxfId="2" priority="121"/>
+  <conditionalFormatting sqref="C473">
+    <cfRule type="duplicateValues" dxfId="2" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C462">
-    <cfRule type="duplicateValues" dxfId="2" priority="120"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C463">
-    <cfRule type="duplicateValues" dxfId="2" priority="118"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C464">
+  <conditionalFormatting sqref="C474">
     <cfRule type="duplicateValues" dxfId="2" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C465">
+  <conditionalFormatting sqref="C475">
+    <cfRule type="duplicateValues" dxfId="2" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C476">
     <cfRule type="duplicateValues" dxfId="2" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C466">
-    <cfRule type="duplicateValues" dxfId="2" priority="111"/>
+  <conditionalFormatting sqref="C477">
+    <cfRule type="duplicateValues" dxfId="2" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C467">
+  <conditionalFormatting sqref="C478">
+    <cfRule type="duplicateValues" dxfId="2" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C479">
     <cfRule type="duplicateValues" dxfId="2" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C468">
-    <cfRule type="duplicateValues" dxfId="2" priority="103"/>
+  <conditionalFormatting sqref="C480">
+    <cfRule type="duplicateValues" dxfId="2" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C469">
-    <cfRule type="duplicateValues" dxfId="2" priority="102"/>
+  <conditionalFormatting sqref="C481">
+    <cfRule type="duplicateValues" dxfId="2" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C470">
+  <conditionalFormatting sqref="C482">
+    <cfRule type="duplicateValues" dxfId="2" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C483">
+    <cfRule type="duplicateValues" dxfId="2" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C484">
+    <cfRule type="duplicateValues" dxfId="2" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C485">
     <cfRule type="duplicateValues" dxfId="2" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C471">
-    <cfRule type="duplicateValues" dxfId="2" priority="97"/>
+  <conditionalFormatting sqref="C486">
+    <cfRule type="duplicateValues" dxfId="2" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C472">
+  <conditionalFormatting sqref="C487">
+    <cfRule type="duplicateValues" dxfId="2" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C488">
+    <cfRule type="duplicateValues" dxfId="2" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C489">
+    <cfRule type="duplicateValues" dxfId="2" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C490">
+    <cfRule type="duplicateValues" dxfId="2" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C491">
+    <cfRule type="duplicateValues" dxfId="2" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C492">
+    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C493">
+    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C494">
+    <cfRule type="duplicateValues" dxfId="2" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C495">
+    <cfRule type="duplicateValues" dxfId="2" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C496">
+    <cfRule type="duplicateValues" dxfId="2" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C497">
+    <cfRule type="duplicateValues" dxfId="2" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C498">
+    <cfRule type="duplicateValues" dxfId="2" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C499">
+    <cfRule type="duplicateValues" dxfId="2" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C500">
+    <cfRule type="duplicateValues" dxfId="2" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C501">
+    <cfRule type="duplicateValues" dxfId="2" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C502">
+    <cfRule type="duplicateValues" dxfId="2" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C503">
+    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C504">
+    <cfRule type="duplicateValues" dxfId="2" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C505">
+    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C527">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C528">
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C529">
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C530">
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C531">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C532">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C533">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C534">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C448">
+    <cfRule type="duplicateValues" dxfId="2" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C450">
+    <cfRule type="duplicateValues" dxfId="2" priority="183"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C452">
+    <cfRule type="duplicateValues" dxfId="2" priority="178"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C455">
+    <cfRule type="duplicateValues" dxfId="2" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C456">
+    <cfRule type="duplicateValues" dxfId="2" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C457">
+    <cfRule type="duplicateValues" dxfId="2" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C460">
+    <cfRule type="duplicateValues" dxfId="2" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C472">
+    <cfRule type="duplicateValues" dxfId="2" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C485">
     <cfRule type="duplicateValues" dxfId="2" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C473">
-    <cfRule type="duplicateValues" dxfId="2" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C474">
-    <cfRule type="duplicateValues" dxfId="2" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C475">
+  <conditionalFormatting sqref="C1:C488">
     <cfRule type="duplicateValues" dxfId="2" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C476">
-    <cfRule type="duplicateValues" dxfId="2" priority="85"/>
+  <conditionalFormatting sqref="C1:C489">
+    <cfRule type="duplicateValues" dxfId="2" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C477">
-    <cfRule type="duplicateValues" dxfId="2" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C478">
-    <cfRule type="duplicateValues" dxfId="2" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C479">
-    <cfRule type="duplicateValues" dxfId="2" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C480">
-    <cfRule type="duplicateValues" dxfId="2" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C481">
-    <cfRule type="duplicateValues" dxfId="2" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C482">
-    <cfRule type="duplicateValues" dxfId="2" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C483">
-    <cfRule type="duplicateValues" dxfId="2" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C484">
-    <cfRule type="duplicateValues" dxfId="2" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C485">
-    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C486">
-    <cfRule type="duplicateValues" dxfId="2" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C487">
-    <cfRule type="duplicateValues" dxfId="2" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C488">
-    <cfRule type="duplicateValues" dxfId="2" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C489">
-    <cfRule type="duplicateValues" dxfId="2" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C490">
-    <cfRule type="duplicateValues" dxfId="2" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C491">
-    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C492">
-    <cfRule type="duplicateValues" dxfId="2" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C493">
-    <cfRule type="duplicateValues" dxfId="2" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C494">
-    <cfRule type="duplicateValues" dxfId="2" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C495">
-    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C496">
-    <cfRule type="duplicateValues" dxfId="2" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C497">
-    <cfRule type="duplicateValues" dxfId="2" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C498">
-    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C499">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C500">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C501">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C502">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C503">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C504">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C505">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C448">
-    <cfRule type="duplicateValues" dxfId="2" priority="159"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C450">
-    <cfRule type="duplicateValues" dxfId="2" priority="154"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C452">
-    <cfRule type="duplicateValues" dxfId="2" priority="149"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C455">
-    <cfRule type="duplicateValues" dxfId="2" priority="142"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C456">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C457">
-    <cfRule type="duplicateValues" dxfId="2" priority="133"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C460">
-    <cfRule type="duplicateValues" dxfId="2" priority="124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C472">
-    <cfRule type="duplicateValues" dxfId="2" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C485">
+  <conditionalFormatting sqref="C1:C493">
     <cfRule type="duplicateValues" dxfId="2" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C488">
+  <conditionalFormatting sqref="C1:C496">
     <cfRule type="duplicateValues" dxfId="2" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C489">
-    <cfRule type="duplicateValues" dxfId="2" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C493">
-    <cfRule type="duplicateValues" dxfId="2" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C496">
-    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C208:C209">
-    <cfRule type="duplicateValues" dxfId="0" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C212:C213">
-    <cfRule type="duplicateValues" dxfId="0" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C215:C216">
-    <cfRule type="duplicateValues" dxfId="0" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219:C220">
-    <cfRule type="duplicateValues" dxfId="0" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="315"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C506:C526">
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C535:C536">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 C4:C91 C93 C95:C145 C147:C206">
-    <cfRule type="duplicateValues" dxfId="0" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="326"/>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D82:E82">
       <formula1>$E$27:$E$30</formula1>
     </dataValidation>
@@ -29695,6 +31492,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q269:Q278">
       <formula1>"无类型,全职,兼职,实习,劳务派遣,退休返聘,劳务外包"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q530:Q533">
+      <formula1>Hidden000cdfc206468fca52c_1_18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D240:E241">
       <formula1>categoryHidden14</formula1>
@@ -30191,21 +31991,12 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 C2 C3">
     <cfRule type="duplicateValues" dxfId="2" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 C2 C3 C4">
     <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 C2 C3 C4 C5">
     <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -30220,7 +32011,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>797</v>
+        <v>853</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -30283,7 +32074,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>798</v>
+        <v>854</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>102</v>
@@ -30335,18 +32126,6 @@
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
     <cfRule type="duplicateValues" dxfId="2" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
